--- a/app/website_monitor/domainler.xlsx
+++ b/app/website_monitor/domainler.xlsx
@@ -589,7 +589,7 @@
         <v>200</v>
       </c>
       <c r="E2" t="n">
-        <v>1726324081.384765</v>
+        <v>1728291214.278681</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -598,11 +598,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.agid.com.tr/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.agid.com.tr/wp-json/wp/v2/pages/5710&gt;; rel="alternate"; type="application/json"'), ('link', '&lt;https://www.agid.com.tr/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:20 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.agid.com.tr/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.agid.com.tr/wp-json/wp/v2/pages/5710&gt;; rel="alternate"; type="application/json"'), ('link', '&lt;https://www.agid.com.tr/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Mon, 07 Oct 2024 08:52:41 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4.471969604492188e-05</v>
+        <v>5.9967041015625e-06</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -650,8 +650,10 @@
           <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>34096</v>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -678,11 +680,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y2" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>28.9497</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -710,7 +716,7 @@
         <v>200</v>
       </c>
       <c r="E3" t="n">
-        <v>1726324083.169273</v>
+        <v>1728291216.499969</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -719,11 +725,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.2.34', 'content-type': 'text/html; charset=UTF-8', 'content-length': '404', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Sat, 14 Sep 2024 14:27:25 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.2.34', 'content-type': 'text/html; charset=UTF-8', 'content-length': '404', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Mon, 07 Oct 2024 08:52:44 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.757883071899414e-05</v>
+        <v>0.0002783694267272949</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -771,8 +777,10 @@
           <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>35210</v>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>35210</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -799,11 +807,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y3" t="n">
-        <v>38.4127</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>27.1384</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>38.4127</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>27.1384</t>
+        </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -831,7 +843,7 @@
         <v>200</v>
       </c>
       <c r="E4" t="n">
-        <v>1726324085.021341</v>
+        <v>1728291219.051817</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -840,11 +852,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '330', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Sat, 14 Sep 2024 14:27:24 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '330', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Mon, 07 Oct 2024 08:52:43 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.619315147399902e-05</v>
+        <v>3.807473182678223e-05</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -857,10 +869,10 @@
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>45507.53944444445</v>
+        <v>45568.53887731482</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>45597.53943287037</v>
+        <v>45658.53886574074</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -869,12 +881,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -884,7 +896,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -892,8 +904,10 @@
           <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v>16250</v>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>20500</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -920,11 +934,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y4" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>29.0601</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>37.7742</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>29.0875</t>
+        </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -952,7 +970,7 @@
         <v>200</v>
       </c>
       <c r="E5" t="n">
-        <v>1726324086.883272</v>
+        <v>1728291221.533915</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -961,15 +979,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '316', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Sat, 14 Sep 2024 14:27:20 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '316', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Mon, 07 Oct 2024 08:52:43 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6.541013717651367e-06</v>
+        <v>0.0001477458477020264</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>www.baskilicocukhalisi.halivizyon.com</t>
+          <t>baskilipaspas.com</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -978,10 +996,10 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>45507.41938657407</v>
+        <v>45568.41949074074</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>45597.419375</v>
+        <v>45658.41947916667</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -990,12 +1008,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1005,7 +1023,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1013,8 +1031,10 @@
           <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v>16250</v>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>20500</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1041,11 +1061,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y5" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>29.0601</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>37.7742</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>29.0875</t>
+        </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1073,7 +1097,7 @@
         <v>301</v>
       </c>
       <c r="E6" t="n">
-        <v>1726324090.063303</v>
+        <v>1728291225.272903</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1082,11 +1106,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'content-length': '795', 'date': 'Sat, 14 Sep 2024 14:27:23 GMT', 'server': 'LiteSpeed', 'location': 'https://www.halifleks.com/', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'content-length': '795', 'date': 'Mon, 07 Oct 2024 08:52:45 GMT', 'server': 'LiteSpeed', 'location': 'https://www.halifleks.com/', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.776312828063965e-05</v>
+        <v>0.0001421422958374023</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1095,14 +1119,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>45497.6791087963</v>
+        <v>45555.69059027778</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>45587.67909722222</v>
+        <v>45645.6905787037</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1134,8 +1158,10 @@
           <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
-      <c r="S6" t="n">
-        <v>34096</v>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1162,11 +1188,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y6" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>28.9497</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1194,7 +1224,7 @@
         <v>200</v>
       </c>
       <c r="E7" t="n">
-        <v>1726324094.197656</v>
+        <v>1728291230.367131</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1203,15 +1233,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=32d30a486a439bcc5b1c4a0a9eae1c2e; expires=Sat, 14-Sep-2024 15:27:21 GMT; Max-Age=3600; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=Neok2GIIe7YL4nLk; expires=Sat, 14-Sep-2024 15:27:21 GMT; Max-Age=3600; path=/; domain=www.camihalicisi.com; secure; HttpOnly'), ('set-cookie', 'store=default; expires=Sun, 14-Sep-2025 14:27:22 GMT; Max-Age=31536000; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:22 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=59d4ff2466d11c21b91a2cf7ecc547f4; expires=Mon, 07-Oct-2024 09:52:44 GMT; Max-Age=3600; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=fE33qpYaqGDq5XVJ; expires=Mon, 07-Oct-2024 09:52:44 GMT; Max-Age=3600; path=/; domain=www.camihalicisi.com; secure; HttpOnly'), ('set-cookie', 'store=default; expires=Tue, 07-Oct-2025 08:52:44 GMT; Max-Age=31536000; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Mon, 07 Oct 2024 08:52:44 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.771377563476562e-05</v>
+        <v>0.0001592025756835938</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>www.camihalicisi.ehalici.com</t>
+          <t>cimrulo.ehalici.com</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1220,10 +1250,10 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>45514.19333333334</v>
+        <v>45572.19288194444</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>45604.19332175926</v>
+        <v>45662.19287037037</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1255,8 +1285,10 @@
           <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
-      <c r="S7" t="n">
-        <v>35210</v>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>35210</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,11 +1315,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y7" t="n">
-        <v>38.4127</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>27.1384</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>38.4127</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>27.1384</t>
+        </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1315,7 +1351,7 @@
         <v>200</v>
       </c>
       <c r="E8" t="n">
-        <v>1726324097.170525</v>
+        <v>1728291233.848748</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1324,27 +1360,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:27:57 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '184', 'date': 'Sat, 14 Sep 2024 14:27:26 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:27:57 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '184', 'date': 'Mon, 07 Oct 2024 08:52:45 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.99980354309082e-06</v>
+        <v>3.596019744873047e-05</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>www.camihalisifabrikasi.camilik.com</t>
+          <t>*.camihalifabrikasi.com</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>45510.68423611111</v>
+        <v>45569.05826388889</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>45600.68422453704</v>
+        <v>45659.05825231481</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1376,8 +1412,10 @@
           <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v>34096</v>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,11 +1442,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y8" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>28.9497</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1436,7 +1478,7 @@
         <v>200</v>
       </c>
       <c r="E9" t="n">
-        <v>1726324099.738607</v>
+        <v>1728291237.192101</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1445,11 +1487,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:28:49 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '192', 'date': 'Sat, 14 Sep 2024 14:27:26 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:28:49 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '192', 'date': 'Mon, 07 Oct 2024 08:52:44 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.754403114318848e-05</v>
+        <v>0.0001812822818756103</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1462,10 +1504,10 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>45510.05806712963</v>
+        <v>45568.30819444444</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>45600.05805555556</v>
+        <v>45658.30818287037</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1497,8 +1539,10 @@
           <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
-      <c r="S9" t="n">
-        <v>34096</v>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,11 +1569,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y9" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>28.9497</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1557,7 +1605,7 @@
         <v>200</v>
       </c>
       <c r="E10" t="n">
-        <v>1726324102.879129</v>
+        <v>1728291240.32472</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1566,27 +1614,27 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:28:10 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '186', 'date': 'Sat, 14 Sep 2024 14:27:22 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:28:10 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '186', 'date': 'Mon, 07 Oct 2024 08:52:44 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4.636502265930176e-05</v>
+        <v>4.16107177734375e-05</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>www.camihalisifabrikasi.camilik.com</t>
+          <t>*.camiihali.com</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>45510.68423611111</v>
+        <v>45568.93478009259</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>45600.68422453704</v>
+        <v>45658.93476851852</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1618,8 +1666,10 @@
           <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
-      <c r="S10" t="n">
-        <v>34096</v>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,11 +1696,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y10" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>28.9497</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1678,7 +1732,7 @@
         <v>200</v>
       </c>
       <c r="E11" t="n">
-        <v>1726324105.685213</v>
+        <v>1728291245.266752</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1687,27 +1741,27 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/5.6.40', 'content-type': 'text/html; charset=UTF-8', 'cache-control': 'no-store, no-cache, must-revalidate, post-check=0, pre-check=0', 'pragma': 'no-cache', 'x-frame-options': 'SAMEORIGIN', 'bubble-fpc': '3.5.1', 'transfer-encoding': 'chunked', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Sat, 14 Sep 2024 14:27:22 GMT', 'server': 'LiteSpeed', 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/5.6.40', 'content-type': 'text/html; charset=UTF-8', 'cache-control': 'no-store, no-cache, must-revalidate, post-check=0, pre-check=0', 'pragma': 'no-cache', 'x-frame-options': 'SAMEORIGIN', 'bubble-fpc': '3.5.1', 'transfer-encoding': 'chunked', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Mon, 07 Oct 2024 08:52:44 GMT', 'server': 'LiteSpeed', 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2.050042152404785e-05</v>
+        <v>8.119058609008789e-05</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>www.camihalisifabrikasi.camilik.com</t>
+          <t>*.camiihali.com</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>45510.68423611111</v>
+        <v>45568.93478009259</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>45600.68422453704</v>
+        <v>45658.93476851852</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1739,8 +1793,10 @@
           <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
-      <c r="S11" t="n">
-        <v>34096</v>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,11 +1823,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y11" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>28.9497</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1799,7 +1859,7 @@
         <v>200</v>
       </c>
       <c r="E12" t="n">
-        <v>1726324108.298545</v>
+        <v>1728291248.292364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1808,15 +1868,15 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Mon, 07 May 2018 08:09:28 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '186', 'date': 'Sat, 14 Sep 2024 14:27:26 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Mon, 07 May 2018 08:09:28 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '186', 'date': 'Mon, 07 Oct 2024 08:52:45 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.55940055847168e-05</v>
+        <v>0.000160405158996582</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>camilik.com</t>
+          <t>*.camilik.com</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1825,10 +1885,10 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>45508.80972222222</v>
+        <v>45567.05854166667</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>45598.80971064815</v>
+        <v>45657.0585300926</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1860,8 +1920,10 @@
           <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>34096</v>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,11 +1950,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y12" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>28.9497</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1908,19 +1974,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>104.247.168.115</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1726324111.199467</v>
+        <v>1726570681.264986</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1929,11 +1995,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/8.1.29'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.carpetsbook.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.carpetsbook.com/wp-json/wp/v2/pages/84&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.carpetsbook.com/&gt;; rel=shortlink'), ('etag', '"8514-1725979052;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('content-length', '24453'), ('date', 'Sat, 14 Sep 2024 14:27:23 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.715755462646484e-05</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1942,18 +2008,18 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>45498.25358796296</v>
+        <v>45556.42932870371</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>45588.25357638889</v>
+        <v>45646.42931712963</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1156euct7.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1978,11 +2044,13 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S13" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2009,11 +2077,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y13" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>28.9497</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2029,19 +2101,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>45.84.190.3</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1726324112.997263</v>
+        <v>1726570682.465205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2050,15 +2122,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.2.34', 'content-type': 'text/html; charset=UTF-8', 'content-length': '402', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Sat, 14 Sep 2024 14:27:26 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.992198944091797e-05</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>bahcecimi.ehalici.com</t>
+          <t>cimrulo.ehalici.com</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2067,24 +2139,24 @@
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>45514.19335648148</v>
+        <v>45572.19288194444</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>45604.19334490741</v>
+        <v>45662.19287037037</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3sazof9.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>İzmir</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>İzmir Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2094,16 +2166,18 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>38.4127,27.1384</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>35210</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2130,11 +2204,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y14" t="n">
-        <v>38.4127</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>27.1384</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2150,19 +2228,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>45.84.190.3</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1726324116.730932</v>
+        <v>1726570685.927641</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2171,41 +2249,41 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.cimtelcit.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.cimtelcit.com/wp-json/wp/v2/pages/22&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.cimtelcit.com/&gt;; rel=shortlink'), ('last-modified', 'Sat, 14 Sep 2024 14:27:23 GMT'), ('cache-control', 'public, max-age=0'), ('expires', 'Sat, 14 Sep 2024 14:27:23 GMT'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent,Accept-Encoding'), ('date', 'Sat, 14 Sep 2024 14:27:23 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.651144027709961e-05</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>www.camihalicisi.ehalici.com</t>
+          <t>cpcontacts.sunicimhali.com</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>45514.19333333334</v>
+        <v>45572.19291666667</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>45604.19332175926</v>
+        <v>45662.19290509259</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3sazof9.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>İzmir</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>İzmir Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2215,16 +2293,18 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>38.4127,27.1384</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>35210</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2251,11 +2331,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y15" t="n">
-        <v>38.4127</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>27.1384</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2271,19 +2355,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1726324119.844066</v>
+        <v>1726570688.278934</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2292,11 +2376,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.confettihalilari.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.confettihalilari.com/wp-json/wp/v2/pages/554&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.confettihalilari.com/&gt;; rel=shortlink'), ('etag', '"2731755-1726310838;br"'), ('x-litespeed-cache', 'hit'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding'), ('date', 'Sat, 14 Sep 2024 14:27:22 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.916670799255371e-05</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2316,17 +2400,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2336,16 +2420,18 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2372,11 +2458,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y16" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>29.0601</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2392,19 +2482,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1726324121.551471</v>
+        <v>1726570689.440717</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2413,11 +2503,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'date': 'Sat, 14 Sep 2024 14:27:27 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3.641104698181152e-05</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2430,24 +2520,24 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>45507.53944444445</v>
+        <v>45568.53887731482</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>45597.53943287037</v>
+        <v>45658.53886574074</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2457,16 +2547,18 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2493,11 +2585,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y17" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>29.0601</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2513,19 +2609,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1726324123.232061</v>
+        <v>1726570690.741832</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2534,15 +2630,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'date': 'Sat, 14 Sep 2024 14:27:22 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.195713043212891e-05</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>www.ucakhalisi.halivizyon.com</t>
+          <t>www.desenlihali.halivizyon.com</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2551,24 +2647,24 @@
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>45507.41946759259</v>
+        <v>45568.41964120371</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>45597.41945601852</v>
+        <v>45658.41962962963</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2578,16 +2674,18 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,11 +2712,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y18" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>29.0601</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2634,19 +2736,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1726324125.168025</v>
+        <v>1726570692.101478</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2655,15 +2757,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'date': 'Sat, 14 Sep 2024 14:27:24 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6.526231765747071e-06</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>www.baskilicocukhalisi.halivizyon.com</t>
+          <t>baskilipaspas.com</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2672,24 +2774,24 @@
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>45507.41938657407</v>
+        <v>45568.41949074074</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>45597.419375</v>
+        <v>45658.41947916667</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2699,16 +2801,18 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2735,11 +2839,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y19" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>29.0601</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2755,19 +2863,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1726324127.120593</v>
+        <v>1726570693.269701</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2776,11 +2884,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '324', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Sat, 14 Sep 2024 14:27:24 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9.494304656982423e-06</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2793,24 +2901,24 @@
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>45507.53944444445</v>
+        <v>45568.53887731482</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>45597.53943287037</v>
+        <v>45658.53886574074</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2820,16 +2928,18 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2856,11 +2966,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y20" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>29.0601</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2876,19 +2990,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1726324128.982651</v>
+        <v>1726570694.711801</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2897,41 +3011,41 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '324', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Sat, 14 Sep 2024 14:27:27 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.905059814453125e-05</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>www.ucuzzemin.halivizyon.com</t>
+          <t>taftinghali.com</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
-        <v>45507.41930555556</v>
+        <v>45568.41954861111</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>45597.41929398148</v>
+        <v>45658.41953703704</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2941,16 +3055,18 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2977,11 +3093,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y21" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>29.0601</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2997,19 +3117,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1726324130.831247</v>
+        <v>1726570695.860456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3018,41 +3138,41 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 15 Jun 2017 10:48:16 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '291', 'date': 'Sat, 14 Sep 2024 14:27:24 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.856302261352539e-05</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>www.baskilicocukhalisi.halivizyon.com</t>
+          <t>www.desenlihali.halivizyon.com</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>45507.41938657407</v>
+        <v>45568.41964120371</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>45597.419375</v>
+        <v>45658.41962962963</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3062,16 +3182,18 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3098,11 +3220,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y22" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>29.0601</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -3118,19 +3244,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1726324134.051179</v>
+        <v>1726570698.370225</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3139,11 +3265,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.dinarsuhalilari.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.dinarsuhalilari.com/wp-json/wp/v2/pages/544&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.dinarsuhalilari.com/&gt;; rel=shortlink'), ('etag', '"2662837-1726016454;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding'), ('content-length', '20314'), ('date', 'Sat, 14 Sep 2024 14:27:24 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.258085250854492e-05</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3163,17 +3289,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3183,16 +3309,18 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3219,11 +3347,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y23" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>29.0601</v>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3239,19 +3371,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89.252.180.102</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>1726324137.165189</v>
+        <v>1726570700.685099</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3260,11 +3392,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=5cf966d11099901b79f58b4ad1bb2e5c; expires=Sat, 14-Sep-2024 15:27:27 GMT; Max-Age=3600; path=/; domain=www.duvardanduvara.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=9tFLXVaQepQOl1wm; expires=Sat, 14-Sep-2024 15:27:27 GMT; Max-Age=3600; path=/; domain=www.duvardanduvara.com; secure; HttpOnly'), ('set-cookie', 'store=default; expires=Sun, 14-Sep-2025 14:27:27 GMT; Max-Age=31536000; path=/; domain=www.duvardanduvara.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.duvardanduvara.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:27 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.75166130065918e-05</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3284,7 +3416,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>102w8oqex.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3309,11 +3441,13 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3340,11 +3474,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y24" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>28.9497</v>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3360,19 +3498,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>104.247.168.115</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1726324139.967252</v>
+        <v>1726570702.744654</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3381,11 +3519,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Tue, 19 Apr 2022 11:39:44 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '5967', 'date': 'Sat, 14 Sep 2024 14:27:30 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.524801254272461e-06</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3398,14 +3536,14 @@
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>45497.67783564814</v>
+        <v>45555.68930555556</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>45587.67782407408</v>
+        <v>45645.68929398148</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1156euct7.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3430,11 +3568,13 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S25" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3461,11 +3601,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y25" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>28.9497</v>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3481,19 +3625,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>45.84.190.3</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1726324143.973303</v>
+        <v>1726570705.812158</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3502,15 +3646,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.ehalici.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.ehalici.com/wp-json/wp/v2/pages/466&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.ehalici.com/&gt;; rel=shortlink'), ('etag', '"400792-1726228889;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('content-length', '23857'), ('date', 'Sat, 14 Sep 2024 14:27:25 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.671099662780762e-05</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ehalici.com</t>
+          <t>cimrulo.ehalici.com</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3519,24 +3663,24 @@
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>45514.19329861111</v>
+        <v>45572.19288194444</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>45604.19328703704</v>
+        <v>45662.19287037037</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3sazof9.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>İzmir</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>İzmir Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3546,16 +3690,18 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>38.4127,27.1384</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S26" t="n">
-        <v>35210</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3582,11 +3728,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y26" t="n">
-        <v>38.4127</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>27.1384</v>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3602,19 +3752,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>104.247.167.211</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1726324148.037051</v>
+        <v>1726570708.888397</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3623,11 +3773,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.emanhali.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.emanhali.com/wp-json/wp/v2/pages/7682&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.emanhali.com/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:24 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3.000020980834961e-06</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3647,7 +3797,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>211hyd4no.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3672,11 +3822,13 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S27" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3703,11 +3855,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y27" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>28.9497</v>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3723,19 +3879,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>89.252.183.35</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1726324151.238472</v>
+        <v>1726570711.048334</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3744,11 +3900,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.emanzemin.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.emanzemin.com/wp-json/wp/v2/pages/11&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.emanzemin.com/&gt;; rel=shortlink'), ('etag', '"8362-1726301402;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('content-length', '41976'), ('date', 'Sat, 14 Sep 2024 14:27:29 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.072811126708985e-06</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3761,14 +3917,14 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>45493.02461805556</v>
+        <v>45551.60317129629</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>45583.02460648148</v>
+        <v>45641.60315972222</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>35rby11p.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3793,11 +3949,13 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S28" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3824,11 +3982,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y28" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>28.9497</v>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -3844,19 +4006,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>89.252.180.102</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1726324153.334027</v>
+        <v>1726570712.262018</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3865,11 +4027,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'cache-control': 'private, no-cache, no-store, must-revalidate, max-age=0', 'pragma': 'no-cache', 'content-type': 'text/html', 'content-length': '1238', 'date': 'Sat, 14 Sep 2024 14:27:28 GMT', 'server': 'LiteSpeed', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4.436159133911133e-05</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3882,14 +4044,14 @@
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>45496.8353125</v>
+        <v>45555.18894675926</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>45586.83530092592</v>
+        <v>45645.18893518519</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>102w8oqex.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3914,11 +4076,13 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S29" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3945,11 +4109,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y29" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>28.9497</v>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -3965,19 +4133,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>89.252.180.102</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1726324156.860409</v>
+        <v>1726570715.508468</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,11 +4154,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.evaminder.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.evaminder.com/wp-json/wp/v2/pages/553&gt;; rel="alternate"; type="application/json"'), ('link', '&lt;https://www.evaminder.com/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:30 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6.067991256713867e-06</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4010,7 +4178,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>102w8oqex.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4035,11 +4203,13 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S30" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4066,11 +4236,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y30" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>28.9497</v>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -4086,19 +4260,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>1726324158.581593</v>
+        <v>1726570716.560016</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4107,15 +4281,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'date': 'Sat, 14 Sep 2024 14:27:24 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.104306221008301e-05</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>www.ucakhalisi.halivizyon.com</t>
+          <t>www.desenlihali.halivizyon.com</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4124,24 +4298,24 @@
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>45507.41946759259</v>
+        <v>45568.41964120371</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>45597.41945601852</v>
+        <v>45658.41962962963</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4151,16 +4325,18 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S31" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4187,11 +4363,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y31" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>29.0601</v>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4207,19 +4387,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>77.37.83.107</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1726324162.269765</v>
+        <v>1726570719.760163</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4228,11 +4408,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Headers({'server': 'hcdn', 'date': 'Sat, 14 Sep 2024 14:27:31 GMT', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'connection': 'keep-alive', 'x-powered-by': 'PHP/8.1.27', 'x-redirect-by': 'WordPress', 'location': 'https://gursoyrealty.com/', 'cache-control': 'public, max-age=604800', 'expires': 'Sat, 21 Sep 2024 14:27:31 GMT', 'x-litespeed-cache': 'miss', 'platform': 'hostinger', 'panel': 'hpanel', 'content-security-policy': 'upgrade-insecure-requests', 'alt-svc': 'h3=":443"; ma=86400', 'x-hcdn-request-id': 'da83363d85e2f19f14b090ce5d39ad1d-srv-edge5', 'x-hcdn-cache-status': 'MISS', 'x-hcdn-upstream-rt': '1.382'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.068801879882813e-05</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -4252,71 +4432,77 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Meppel</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Drenthe</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>52.6958,6.1944</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>AS47583 Hostinger International Limited</t>
-        </is>
-      </c>
-      <c r="S32" t="n">
-        <v>7941</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Europe/Amsterdam</t>
+          <t>Europe/Istanbul</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="Y32" t="n">
-        <v>52.6958</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>6.1944</v>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/NL.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
         </is>
       </c>
     </row>
@@ -4328,19 +4514,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>89.252.183.211</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1726324164.784506</v>
+        <v>1726570721.397102</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4349,11 +4535,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'set-cookie': 'PHPSESSID=6536beb727835566b308a8e0cc3ec08c; path=/; HttpOnly; secure', 'expires': 'Thu, 19 Nov 1981 08:52:00 GMT', 'cache-control': 'no-store, no-cache, must-revalidate', 'pragma': 'no-cache', 'content-type': 'text/html; charset=UTF-8', 'transfer-encoding': 'chunked', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Sat, 14 Sep 2024 14:27:24 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.780390739440918e-05</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -4373,7 +4559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>211km5vaq.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4398,11 +4584,13 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S33" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4429,11 +4617,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y33" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>28.9497</v>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -4449,19 +4641,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1726324166.685874</v>
+        <v>1726570722.737031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4470,41 +4662,41 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 15 Jun 2017 10:57:31 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '296', 'date': 'Sat, 14 Sep 2024 14:27:27 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.864528656005859e-05</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>www.ucuzzemin.halivizyon.com</t>
+          <t>baskilipaspas.com</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K34" s="2" t="n">
-        <v>45507.41930555556</v>
+        <v>45568.41949074074</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>45597.41929398148</v>
+        <v>45658.41947916667</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4514,16 +4706,18 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S34" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4550,11 +4744,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y34" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>29.0601</v>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -4570,19 +4768,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1726324168.807063</v>
+        <v>1726570723.904348</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4591,15 +4789,15 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Mon, 03 Jul 2017 12:40:28 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '281', 'date': 'Sat, 14 Sep 2024 14:27:27 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.683855056762695e-05</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>www.ucakhalisi.halivizyon.com</t>
+          <t>www.desenlihali.halivizyon.com</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4608,24 +4806,24 @@
         </is>
       </c>
       <c r="K35" s="2" t="n">
-        <v>45507.41946759259</v>
+        <v>45568.41964120371</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>45597.41945601852</v>
+        <v>45658.41962962963</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4635,16 +4833,18 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S35" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4671,11 +4871,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y35" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>29.0601</v>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -4691,19 +4895,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>104.247.167.211</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1726324171.771503</v>
+        <v>1726570725.832482</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4712,11 +4916,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'cache-control': 'no-store, no-cache, must-revalidate, post-check=0, pre-check=0', 'pragma': 'no-cache', 'x-frame-options': 'SAMEORIGIN', 'bubble-fpc': '3.5.1', 'content-length': '13277', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Sat, 14 Sep 2024 14:27:23 GMT', 'server': 'LiteSpeed', 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6.021261215209961e-06</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -4736,7 +4940,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>211hyd4no.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4761,11 +4965,13 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S36" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4792,11 +4998,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y36" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>28.9497</v>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
@@ -4812,19 +5022,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>45.84.190.3</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1726324173.49436</v>
+        <v>1726570726.982428</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4833,41 +5043,41 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.2.34', 'content-type': 'text/html; charset=UTF-8', 'content-length': '404', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Sat, 14 Sep 2024 14:27:25 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4.802823066711426e-05</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ehalici.com</t>
+          <t>cpcontacts.sunicimhali.com</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>45514.19329861111</v>
+        <v>45572.19291666667</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>45604.19328703704</v>
+        <v>45662.19290509259</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3sazof9.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>İzmir</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>İzmir Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4877,16 +5087,18 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>38.4127,27.1384</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S37" t="n">
-        <v>35210</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4913,11 +5125,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y37" t="n">
-        <v>38.4127</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>27.1384</v>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -4933,19 +5149,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>104.247.168.115</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1726324176.210315</v>
+        <v>1726570728.923438</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4954,11 +5170,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/8.1.29'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.haliutubandi.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.haliutubandi.com/wp-json/wp/v2/pages/1263&gt;; rel="alternate"; type="application/json"'), ('link', '&lt;https://www.haliutubandi.com/&gt;; rel=shortlink'), ('etag', '"8625-1726016669;br"'), ('x-litespeed-cache', 'hit'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:29 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.803398132324219e-05</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4971,14 +5187,14 @@
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>45497.67818287037</v>
+        <v>45555.68976851852</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>45587.6781712963</v>
+        <v>45645.68975694444</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1156euct7.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5003,11 +5219,13 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S38" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5034,11 +5252,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y38" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>28.9497</v>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -5054,19 +5276,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1726324179.419743</v>
+        <v>1726570731.075528</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5075,11 +5297,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.halivizyon.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.halivizyon.com/wp-json/wp/v2/pages/97&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.halivizyon.com/&gt;; rel=shortlink'), ('etag', '"2668688-1726036173;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding'), ('content-length', '15357'), ('date', 'Sat, 14 Sep 2024 14:27:27 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.784825325012207e-05</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -5099,17 +5321,17 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5119,16 +5341,18 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S39" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5155,11 +5379,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y39" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>29.0601</v>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -5175,19 +5403,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>104.247.168.115</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>1726324183.948735</v>
+        <v>1726570734.946724</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5196,11 +5424,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/8.1.29'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.haliyapistirici.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.haliyapistirici.com/wp-json/wp/v2/pages/1263&gt;; rel="alternate"; type="application/json"'), ('link', '&lt;https://www.haliyapistirici.com/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:33 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2.205967903137207e-05</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -5213,14 +5441,14 @@
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>45498.25304398148</v>
+        <v>45556.42857638889</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>45588.25303240741</v>
+        <v>45646.42856481481</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1156euct7.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5245,11 +5473,13 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S40" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5276,11 +5506,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y40" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>28.9497</v>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -5296,19 +5530,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>51.195.87.128</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1726324186.706242</v>
+        <v>1726570737.055303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5317,11 +5551,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=4b39f9f49a9c6c3f18d342bd18dee0f8; expires=Sat, 14-Sep-2024 15:27:28 GMT; Max-Age=3600; path=/; domain=www.hediyepaspas.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=tAccgJgRt8ZHCJ7s; expires=Sat, 14-Sep-2024 15:27:28 GMT; Max-Age=3600; path=/; domain=www.hediyepaspas.com; secure; HttpOnly'), ('set-cookie', 'store=default; expires=Sun, 14-Sep-2025 14:27:28 GMT; Max-Age=31536000; path=/; domain=www.hediyepaspas.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.hediyepaspas.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:28 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4.291987419128418e-05</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -5334,78 +5568,84 @@
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>45505.1150462963</v>
+        <v>45563.09626157407</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>45595.11503472222</v>
+        <v>45653.09625</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>ip128.ip-51-195-87.eu</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>50.1155,8.6842</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>AS16276 OVH SAS</t>
-        </is>
-      </c>
-      <c r="S41" t="n">
-        <v>60306</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Europe/Berlin</t>
+          <t>Europe/Istanbul</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="Y41" t="n">
-        <v>50.1155</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>8.684200000000001</v>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
         </is>
       </c>
     </row>
@@ -5417,19 +5657,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>89.252.180.162</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1726324190.647203</v>
+        <v>1726570739.982847</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5438,15 +5678,15 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/5.6.40', 'content-type': 'text/html; charset=UTF-8', 'cache-control': 'no-store, no-cache, must-revalidate, post-check=0, pre-check=0', 'pragma': 'no-cache', 'x-frame-options': 'SAMEORIGIN', 'bubble-fpc': '3.5.1', 'content-length': '15225', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Sat, 14 Sep 2024 14:27:26 GMT', 'server': 'LiteSpeed', 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3.034830093383789e-06</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>www.hotelhalilari.camilik.com</t>
+          <t>*.camiihali.com</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5455,14 +5695,14 @@
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>45510.80810185185</v>
+        <v>45568.93478009259</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>45600.80809027778</v>
+        <v>45658.93476851852</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>162p94xyd.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5487,11 +5727,13 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S42" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5518,11 +5760,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y42" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>28.9497</v>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -5538,19 +5784,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>89.252.180.102</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1726324192.32918</v>
+        <v>1726570741.194142</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5559,11 +5805,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'cache-control': 'private, no-cache, no-store, must-revalidate, max-age=0', 'pragma': 'no-cache', 'content-type': 'text/html', 'content-length': '1238', 'date': 'Sat, 14 Sep 2024 14:27:29 GMT', 'server': 'LiteSpeed', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.311801910400391e-05</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -5583,7 +5829,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>102w8oqex.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5608,11 +5854,13 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S43" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5639,11 +5887,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y43" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>28.9497</v>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -5659,19 +5911,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>89.252.180.102</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1726324195.028032</v>
+        <v>1726570743.040118</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5680,11 +5932,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'cache-control': 'no-store, no-cache, must-revalidate, post-check=0, pre-check=0', 'pragma': 'no-cache', 'x-frame-options': 'SAMEORIGIN', 'bubble-fpc': '3.5.1', 'transfer-encoding': 'chunked', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Sat, 14 Sep 2024 14:27:27 GMT', 'server': 'LiteSpeed', 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>4.795098304748535e-05</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -5693,18 +5945,18 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>45508.34420138889</v>
+        <v>45566.9482175926</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>45598.34418981482</v>
+        <v>45656.94820601852</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>102w8oqex.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5729,11 +5981,13 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S44" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5760,11 +6014,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y44" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>28.9497</v>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -5780,19 +6038,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>51.195.87.128</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1726324197.75362</v>
+        <v>1726570744.876788</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5801,11 +6059,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 09 May 2024 12:59:28 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '15617', 'date': 'Sat, 14 Sep 2024 14:27:28 GMT', 'server': 'LiteSpeed', 'cache-control': 'max-age=0, no-cache, no-store, must-revalidate', 'pragma': 'no-cache', 'expires': 'Mon, 29 Oct 1923 20:30:00 GMT', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2.803683280944824e-05</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -5825,71 +6083,77 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>ip128.ip-51-195-87.eu</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>50.1155,8.6842</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>AS16276 OVH SAS</t>
-        </is>
-      </c>
-      <c r="S45" t="n">
-        <v>60306</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Europe/Berlin</t>
+          <t>Europe/Istanbul</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="Y45" t="n">
-        <v>50.1155</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>8.684200000000001</v>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
         </is>
       </c>
     </row>
@@ -5901,19 +6165,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>51.195.87.128</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1726324202.852735</v>
+        <v>1726570748.58509</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5922,11 +6186,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'content-length': '795', 'date': 'Sat, 14 Sep 2024 14:27:28 GMT', 'server': 'LiteSpeed', 'location': 'https://www.karohalicim.com/tr/', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.533861160278321e-06</v>
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -5946,71 +6210,77 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>ip128.ip-51-195-87.eu</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>50.1155,8.6842</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>AS16276 OVH SAS</t>
-        </is>
-      </c>
-      <c r="S46" t="n">
-        <v>60306</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Europe/Berlin</t>
+          <t>Europe/Istanbul</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="Y46" t="n">
-        <v>50.1155</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>8.684200000000001</v>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
         </is>
       </c>
     </row>
@@ -6022,19 +6292,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>89.252.183.211</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1726324205.928396</v>
+        <v>1726570750.707183</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6043,11 +6313,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.karokaucukzemin.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.karokaucukzemin.com/wp-json/wp/v2/pages/633&gt;; rel="alternate"; type="application/json"'), ('link', '&lt;https://www.karokaucukzemin.com/&gt;; rel=shortlink'), ('etag', '"1338-1725921404;br"'), ('x-litespeed-cache', 'hit'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:24 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.468441009521484e-05</v>
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -6060,14 +6330,14 @@
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>45506.48365740741</v>
+        <v>45564.8384375</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>45596.48364583333</v>
+        <v>45654.83842592593</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>211km5vaq.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6092,11 +6362,13 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S47" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6123,11 +6395,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y47" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>28.9497</v>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
@@ -6143,19 +6419,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1726324207.981002</v>
+        <v>1726570751.92368</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6164,15 +6440,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 15 Jun 2017 11:00:18 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '294', 'date': 'Sat, 14 Sep 2024 14:27:27 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.752257347106934e-05</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>www.baskilicocukhalisi.halivizyon.com</t>
+          <t>baskilipaspas.com</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6181,24 +6457,24 @@
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>45507.41938657407</v>
+        <v>45568.41949074074</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>45597.419375</v>
+        <v>45658.41947916667</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6208,16 +6484,18 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S48" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6244,11 +6522,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y48" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>29.0601</v>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6264,19 +6546,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>89.252.183.211</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1726324210.725858</v>
+        <v>1726570753.645363</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6285,11 +6567,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'set-cookie': 'PHPSESSID=9f03fbe791e0c7aac2f16f0560a58d4f; path=/; HttpOnly; secure', 'expires': 'Thu, 19 Nov 1981 08:52:00 GMT', 'cache-control': 'no-store, no-cache, must-revalidate', 'pragma': 'no-cache', 'content-type': 'text/html; charset=UTF-8', 'transfer-encoding': 'chunked', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Sat, 14 Sep 2024 14:27:24 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.611781120300293e-05</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -6309,7 +6591,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>211km5vaq.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6334,11 +6616,13 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S49" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6365,11 +6649,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y49" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>28.9497</v>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -6385,19 +6673,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>89.252.183.211</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1726324213.213481</v>
+        <v>1726570755.372984</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6406,11 +6694,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'set-cookie': 'PHPSESSID=946f49457c8824e31d064c391a7458f2; path=/; HttpOnly; secure', 'expires': 'Thu, 19 Nov 1981 08:52:00 GMT', 'cache-control': 'no-store, no-cache, must-revalidate', 'pragma': 'no-cache', 'content-type': 'text/html; charset=UTF-8', 'content-length': '11510', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Sat, 14 Sep 2024 14:27:24 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.420615196228027e-05</v>
+        <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -6430,7 +6718,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>211km5vaq.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6455,11 +6743,13 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S50" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6486,11 +6776,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y50" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>28.9497</v>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -6506,19 +6800,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>89.252.183.211</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>1726324216.419449</v>
+        <v>1726570757.506343</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6527,11 +6821,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.mescithalisi.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.mescithalisi.com/wp-json/wp/v2/pages/6019131&gt;; rel="alternate"; type="application/json"'), ('link', '&lt;https://www.mescithalisi.com/&gt;; rel=shortlink'), ('etag', '"1330-1725917482;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('content-length', '24152'), ('date', 'Sat, 14 Sep 2024 14:27:24 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.812410354614258e-05</v>
+        <v>0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -6551,7 +6845,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>211km5vaq.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6576,11 +6870,13 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S51" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6607,11 +6903,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y51" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>28.9497</v>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -6627,19 +6927,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>89.252.183.211</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1726324219.413915</v>
+        <v>1726570759.537582</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6648,11 +6948,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.mineflocu.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.mineflocu.com/wp-json/wp/v2/pages/7366&gt;; rel="alternate"; type="application/json"'), ('link', '&lt;https://www.mineflocu.com/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:25 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.771903038024902e-05</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -6672,7 +6972,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>211km5vaq.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6697,11 +6997,13 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S52" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6728,11 +7030,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y52" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>28.9497</v>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -6748,19 +7054,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>185.106.210.162</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1726324222.160018</v>
+        <v>1726570761.513508</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6769,11 +7075,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/8.2.22'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.myfloor.com.tr/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.myfloor.com.tr/wp-json/wp/v2/pages/7105&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.myfloor.com.tr/&gt;; rel=shortlink'), ('server-timing', 'wp-before-template;dur=1708.39'), ('etag', '"6175-1726258110;br"'), ('x-litespeed-cache', 'hit'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:26 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2.932262420654297e-05</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -6793,7 +7099,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>162uzpsk0.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6818,11 +7124,13 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S53" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6849,11 +7157,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y53" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>28.9497</v>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -6869,19 +7181,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>51.195.87.128</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>1726324225.028288</v>
+        <v>1726570763.41641</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6890,11 +7202,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=8df5bbc808870436cb5c0c589212e0d1; expires=Sat, 14-Sep-2024 15:27:27 GMT; Max-Age=3600; path=/; domain=www.paspasfabrikasi.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=x67F0d2HbyOQym8N; expires=Sat, 14-Sep-2024 15:27:27 GMT; Max-Age=3600; path=/; domain=www.paspasfabrikasi.com; secure; HttpOnly'), ('set-cookie', 'store=default; expires=Sun, 14-Sep-2025 14:27:27 GMT; Max-Age=31536000; path=/; domain=www.paspasfabrikasi.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.paspasfabrikasi.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:27 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>3.526878356933594e-05</v>
+        <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -6914,71 +7226,77 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>ip128.ip-51-195-87.eu</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>50.1155,8.6842</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>AS16276 OVH SAS</t>
-        </is>
-      </c>
-      <c r="S54" t="n">
-        <v>60306</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Europe/Berlin</t>
+          <t>Europe/Istanbul</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="Y54" t="n">
-        <v>50.1155</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>8.684200000000001</v>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
         </is>
       </c>
     </row>
@@ -6990,19 +7308,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1726324227.034806</v>
+        <v>1726570764.78545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7011,41 +7329,41 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 15 Jun 2017 11:07:34 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '291', 'date': 'Sat, 14 Sep 2024 14:27:27 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>2.017498016357422e-05</v>
+        <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>www.ucakhalisi.halivizyon.com</t>
+          <t>taftinghali.com</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K55" s="2" t="n">
-        <v>45507.41946759259</v>
+        <v>45568.41954861111</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>45597.41945601852</v>
+        <v>45658.41953703704</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7055,16 +7373,18 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S55" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7091,11 +7411,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y55" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>29.0601</v>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -7111,19 +7435,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1726324228.976455</v>
+        <v>1726570766.230831</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7132,41 +7456,41 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 15 Jun 2017 11:08:04 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '291', 'date': 'Sat, 14 Sep 2024 14:27:25 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.0001790573596954346</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>www.ucuzzemin.halivizyon.com</t>
+          <t>taftinghali.com</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K56" s="2" t="n">
-        <v>45507.41930555556</v>
+        <v>45568.41954861111</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>45597.41929398148</v>
+        <v>45658.41953703704</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7176,16 +7500,18 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S56" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7212,11 +7538,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y56" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>29.0601</v>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -7232,19 +7562,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>1726324231.075934</v>
+        <v>1726570767.621725</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7253,11 +7583,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 15 Jun 2017 11:09:18 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '299', 'date': 'Sat, 14 Sep 2024 14:27:27 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1.605439186096191e-05</v>
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -7277,17 +7607,17 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7297,16 +7627,18 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S57" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7333,11 +7665,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y57" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>29.0601</v>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -7353,19 +7689,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1726324238.614809</v>
+        <v>1726570772.053338</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7374,11 +7710,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.samurhalilari.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.samurhalilari.com/wp-json/wp/v2/pages/1043&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.samurhalilari.com/&gt;; rel=shortlink'), ('etag', '"2659206-1726002716;br"'), ('x-litespeed-cache', 'hit'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding'), ('date', 'Sat, 14 Sep 2024 14:27:24 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1.903247833251953e-05</v>
+        <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -7398,17 +7734,17 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7418,16 +7754,18 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S58" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7454,11 +7792,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y58" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>29.0601</v>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -7474,19 +7816,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>185.106.210.162</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1726324241.753245</v>
+        <v>1726570774.456992</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7495,11 +7837,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/8.2.23', 'set-cookie': 'PHPSESSID=lo4rle5krma7tsf63i7njdtk47; expires=Sat, 14 Sep 2024 15:27:27 GMT; Max-Age=3600; path=/; domain=www.stepmat.com.tr; secure; HttpOnly; SameSite=Lax', 'pragma': 'no-cache', 'cache-control': 'max-age=0, must-revalidate, no-cache, no-store', 'expires': 'Thu, 14 Sep 2023 11:21:00 GMT', 'content-security-policy-report-only': "font-src data: 'self' 'unsafe-inline'; form-action geostag.cardinalcommerce.com geo.cardinalcommerce.com 1eafstag.cardinalcommerce.com 1eaf.cardinalcommerce.com centinelapistag.cardinalcommerce.com centinelapi.cardinalcommerce.com pilot-payflowlink.paypal.com www.paypal.com www.sandbox.paypal.com *.cardinalcommerce.com *.paypal.com 3ds-secure.cardcomplete.com www.clicksafe.lloydstsb.com pay.activa-card.com *.wirecard.com acs.sia.eu *.touchtechpayments.com www.securesuite.co.uk rsa3dsauth.com *.monzo.com *.arcot.com *.wlp-acs.com * 'self' 'unsafe-inline'; frame-ancestors 'self'; frame-src fast.amc.demdex.net *.adobe.com bid.g.doubleclick.net *.youtube.com *.youtube-nocookie.com geostag.cardinalcommerce.com geo.cardinalcommerce.com 1eafstag.cardinalcommerce.com 1eaf.cardinalcommerce.com centinelapistag.cardinalcommerce.com centinelapi.cardinalcommerce.com www.paypal.com www.sandbox.paypal.com pilot-payflowlink.paypal.com player.vimeo.com https://www.google.com/recaptcha/ c.paypal.com checkout.paypal.com assets.braintreegateway.com pay.google.com *.cardinalcommerce.com *.paypal.com * 'self' 'unsafe-inline'; img-src assets.adobedtm.com amcglobal.sc.omtrdc.net dpm.demdex.net cm.everesttech.net *.adobe.com widgets.magentocommerce.com data: www.googleadservices.com www.google-analytics.com googleads.g.doubleclick.net www.google.com bid.g.doubleclick.net analytics.google.com www.googletagmanager.com *.ftcdn.net *.behance.net t.paypal.com www.paypal.com www.paypalobjects.com fpdbs.paypal.com fpdbs.sandbox.paypal.com *.vimeocdn.com i.ytimg.com *.youtube.com validator.swagger.io www.sandbox.paypal.com b.stats.paypal.com dub.stats.paypal.com assets.braintreegateway.com c.paypal.com checkout.paypal.com *.paypal.com data: 'self' 'unsafe-inline'; script-src assets.adobedtm.com *.adobe.com www.googleadservices.com www.google-analytics.com googleads.g.doubleclick.net analytics.google.com www.googletagmanager.com *.newrelic.com *.nr-data.net geostag.cardinalcommerce.com 1eafstag.cardinalcommerce.com geoapi.cardinalcommerce.com 1eafapi.cardinalcommerce.com songbird.cardinalcommerce.com includestest.ccdc02.com www.paypal.com www.sandbox.paypal.com www.paypalobjects.com t.paypal.com s.ytimg.com www.googleapis.com vimeo.com www.vimeo.com *.vimeocdn.com *.youtube.com https://www.gstatic.com/recaptcha/ https://www.google.com/recaptcha/ js.braintreegateway.com assets.braintreegateway.com c.paypal.com pay.google.com api.braintreegateway.com api.sandbox.braintreegateway.com client-analytics.braintreegateway.com client-analytics.sandbox.braintreegateway.com *.paypal.com songbirdstag.cardinalcommerce.com 'self' 'unsafe-inline' 'unsafe-eval'; style-src *.adobe.com unsafe-inline assets.braintreegateway.com 'self' 'unsafe-inline'; object-src 'self' 'unsafe-inline'; media-src *.adobe.com 'self' 'unsafe-inline'; manifest-src 'self' 'unsafe-inline'; connect-src dpm.demdex.net amcglobal.sc.omtrdc.net www.google-analytics.com www.googleadservices.com analytics.google.com www.googletagmanager.com *.newrelic.com *.nr-data.net vimeo.com geostag.cardinalcommerce.com geo.cardinalcommerce.com 1eafstag.cardinalcommerce.com 1eaf.cardinalcommerce.com centinelapistag.cardinalcommerce.com centinelapi.cardinalcommerce.com www.sandbox.paypal.com www.paypalobjects.com www.paypal.com pilot-payflowlink.paypal.com api.braintreegateway.com api.sandbox.braintreegateway.com client-analytics.braintreegateway.com client-analytics.sandbox.braintreegateway.com *.braintree-api.com *.paypal.com *.cardinalcommerce.com *.google.com google.com 'self' 'unsafe-inline'; child-src assets.braintreegateway.com c.paypal.com *.paypal.com http: https: blob: 'self' 'unsafe-inline'; default-src 'self' 'unsafe-inline' 'unsafe-eval'; base-uri 'self' 'unsafe-inline';", 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'x-frame-options': 'SAMEORIGIN', 'content-type': 'text/html; charset=UTF-8', 'transfer-encoding': 'chunked', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Sat, 14 Sep 2024 14:27:27 GMT', 'server': 'LiteSpeed', 'x-ua-compatible': 'IE=edge', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.03397274017334e-05</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -7519,7 +7861,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>162uzpsk0.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -7544,11 +7886,13 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S59" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7575,11 +7919,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y59" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>28.9497</v>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -7595,19 +7943,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>45.84.190.3</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>1726324243.843842</v>
+        <v>1726570775.681856</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7616,41 +7964,41 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.2.34', 'content-type': 'text/html; charset=UTF-8', 'content-length': '404', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Sat, 14 Sep 2024 14:27:25 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>3.331065177917481e-05</v>
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>www.camihalicisi.ehalici.com</t>
+          <t>cpcontacts.sunicimhali.com</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>45514.19333333334</v>
+        <v>45572.19291666667</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>45604.19332175926</v>
+        <v>45662.19290509259</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>3sazof9.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>İzmir</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>İzmir Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7660,16 +8008,18 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>38.4127,27.1384</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S60" t="n">
-        <v>35210</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7696,11 +8046,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y60" t="n">
-        <v>38.4127</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>27.1384</v>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -7716,19 +8070,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1726324245.726923</v>
+        <v>1726570776.964494</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7737,41 +8091,41 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Tue, 02 Jul 2019 11:53:54 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '179', 'date': 'Sat, 14 Sep 2024 14:27:27 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.558707237243652e-05</v>
+        <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>www.ucuzzemin.halivizyon.com</t>
+          <t>taftinghali.com</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
-        <v>45507.41930555556</v>
+        <v>45568.41954861111</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>45597.41929398148</v>
+        <v>45658.41953703704</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7781,16 +8135,18 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S61" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7817,11 +8173,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y61" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>29.0601</v>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -7837,19 +8197,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1726324248.861084</v>
+        <v>1726570779.295804</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7858,41 +8218,41 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Tue, 02 Jul 2019 12:23:00 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '195', 'date': 'Sat, 14 Sep 2024 14:27:24 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.015995025634766e-06</v>
+        <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>www.baskilicocukhalisi.halivizyon.com</t>
+          <t>www.desenlihali.halivizyon.com</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
-        <v>45507.41938657407</v>
+        <v>45568.41964120371</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>45597.419375</v>
+        <v>45658.41962962963</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7902,16 +8262,18 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S62" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7938,11 +8300,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y62" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>29.0601</v>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -7958,19 +8324,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>89.252.183.211</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1726324251.475836</v>
+        <v>1726570781.074097</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7979,11 +8345,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.tatamiminder.net/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.tatamiminder.net/wp-json/wp/v2/pages/553&gt;; rel="alternate"; type="application/json"'), ('link', '&lt;https://www.tatamiminder.net/&gt;; rel=shortlink'), ('etag', '"1324-1725913052;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('content-length', '20870'), ('date', 'Sat, 14 Sep 2024 14:27:24 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2.858424186706543e-05</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -8003,7 +8369,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>211km5vaq.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8028,11 +8394,13 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S63" t="n">
-        <v>34096</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8059,11 +8427,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y63" t="n">
-        <v>41.0138</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>28.9497</v>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -8079,19 +8451,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>1726324253.963605</v>
+        <v>1726570782.631825</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8100,15 +8472,15 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Tue, 02 Jul 2019 12:29:08 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '195', 'date': 'Sat, 14 Sep 2024 14:27:25 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.464199066162109e-05</v>
+        <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>www.ucakhalisi.halivizyon.com</t>
+          <t>www.desenlihali.halivizyon.com</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8117,24 +8489,24 @@
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>45507.41946759259</v>
+        <v>45568.41964120371</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>45597.41945601852</v>
+        <v>45658.41962962963</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8144,16 +8516,18 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S64" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8180,11 +8554,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y64" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>29.0601</v>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -8200,19 +8578,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>1726324257.309598</v>
+        <v>1726570786.761294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8221,11 +8599,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.turkfleks.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.turkfleks.com/wp-json/wp/v2/pages/875&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.turkfleks.com/&gt;; rel=shortlink'), ('etag', '"2669301-1726037791;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding'), ('content-length', '23619'), ('date', 'Sat, 14 Sep 2024 14:27:27 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>6.591558456420898e-06</v>
+        <v>0</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -8245,17 +8623,17 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8265,16 +8643,18 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S65" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8301,11 +8681,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y65" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>29.0601</v>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -8321,19 +8705,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>31.192.212.112</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1726324259.040612</v>
+        <v>1726570787.84602</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8342,41 +8726,41 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'date': 'Sat, 14 Sep 2024 14:27:27 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>3.356385231018066e-05</v>
+        <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>www.ucakhalisi.halivizyon.com</t>
+          <t>taftinghali.com</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K66" s="2" t="n">
-        <v>45507.41946759259</v>
+        <v>45568.41954861111</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>45597.41945601852</v>
+        <v>45658.41953703704</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>112zop6uj.guzel.net.tr</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Bursa Province</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8386,16 +8770,18 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>40.1956,29.0601</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
-        </is>
-      </c>
-      <c r="S66" t="n">
-        <v>16250</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8422,11 +8808,15 @@
           <t>AS</t>
         </is>
       </c>
-      <c r="Y66" t="n">
-        <v>40.1956</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>29.0601</v>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -8442,19 +8832,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>51.195.87.128</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>1726324264.551573</v>
+        <v>1726570791.510156</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8463,11 +8853,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'content-length': '795', 'date': 'Sat, 14 Sep 2024 14:27:29 GMT', 'server': 'LiteSpeed', 'location': 'https://www.ucuzkarohalilar.com/tr/', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1.768994331359863e-05</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -8487,71 +8877,77 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>ip128.ip-51-195-87.eu</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>50.1155,8.6842</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>AS16276 OVH SAS</t>
-        </is>
-      </c>
-      <c r="S67" t="n">
-        <v>60306</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Europe/Berlin</t>
+          <t>Europe/Istanbul</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="Y67" t="n">
-        <v>50.1155</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>8.684200000000001</v>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
         </is>
       </c>
     </row>
@@ -8563,19 +8959,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>51.195.87.128</t>
+          <t>IP Not Found</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1726324267.69665</v>
+        <v>1726570793.459229</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8584,11 +8980,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=8bcfc0d89008814f17624bf3340faaf3; expires=Sat, 14-Sep-2024 15:27:29 GMT; Max-Age=3600; path=/; domain=www.zeminbank.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=3b9eE6jR5z9yR3cm; expires=Sat, 14-Sep-2024 15:27:29 GMT; Max-Age=3600; path=/; domain=www.zeminbank.com; secure; HttpOnly'), ('set-cookie', 'store=tr_tr; expires=Sun, 14-Sep-2025 14:27:29 GMT; Max-Age=31536000; path=/; domain=www.zeminbank.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.zeminbank.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Sat, 14 Sep 2024 14:27:29 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>4.199504852294922e-05</v>
+        <v>0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -8601,78 +8997,84 @@
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>45505.11539351852</v>
+        <v>45563.0966550926</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>45595.11538194444</v>
+        <v>45653.09664351852</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>ip128.ip-51-195-87.eu</t>
+          <t>130.107.146.159.srv.turk.net</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Hesse</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>50.1155,8.6842</t>
+          <t>41.0138,28.9497</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>AS16276 OVH SAS</t>
-        </is>
-      </c>
-      <c r="S68" t="n">
-        <v>60306</v>
+          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>34096</t>
+        </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Europe/Berlin</t>
+          <t>Europe/Istanbul</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TRY</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="Y68" t="n">
-        <v>50.1155</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>8.684200000000001</v>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>41.0138</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>28.9497</t>
+        </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
         </is>
       </c>
     </row>

--- a/app/website_monitor/domainler.xlsx
+++ b/app/website_monitor/domainler.xlsx
@@ -589,7 +589,7 @@
         <v>200</v>
       </c>
       <c r="E2" t="n">
-        <v>1728291214.278681</v>
+        <v>1731573770.570007</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -598,11 +598,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.agid.com.tr/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.agid.com.tr/wp-json/wp/v2/pages/5710&gt;; rel="alternate"; type="application/json"'), ('link', '&lt;https://www.agid.com.tr/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Mon, 07 Oct 2024 08:52:41 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.agid.com.tr/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.agid.com.tr/wp-json/wp/v2/pages/5710&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.agid.com.tr/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:08 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5.9967041015625e-06</v>
+        <v>6.997823715209961e-06</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>45541.935625</v>
+        <v>45600.01020833333</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>45631.93561342593</v>
+        <v>45690.01019675926</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>200</v>
       </c>
       <c r="E3" t="n">
-        <v>1728291216.499969</v>
+        <v>1731573772.135333</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -725,27 +725,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.2.34', 'content-type': 'text/html; charset=UTF-8', 'content-length': '404', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Mon, 07 Oct 2024 08:52:44 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.2.34', 'content-type': 'text/html; charset=UTF-8', 'content-length': '404', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Thu, 14 Nov 2024 08:42:07 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.0002783694267272949</v>
+        <v>4.406356811523438e-05</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>bahcecimi.ehalici.com</t>
+          <t>otelhalicisi.ehalici.com</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>45516.31628472222</v>
+        <v>45574.44202546297</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>45606.31627314815</v>
+        <v>45664.44201388889</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>200</v>
       </c>
       <c r="E4" t="n">
-        <v>1728291219.051817</v>
+        <v>1731573773.936117</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -852,11 +852,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '330', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Mon, 07 Oct 2024 08:52:43 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '330', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Thu, 14 Nov 2024 08:42:06 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.807473182678223e-05</v>
+        <v>2.79998779296875e-05</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>200</v>
       </c>
       <c r="E5" t="n">
-        <v>1728291221.533915</v>
+        <v>1731573775.667627</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '316', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Mon, 07 Oct 2024 08:52:43 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '316', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Thu, 14 Nov 2024 08:42:06 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.0001477458477020264</v>
+        <v>7.112503051757813e-06</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>301</v>
       </c>
       <c r="E6" t="n">
-        <v>1728291225.272903</v>
+        <v>1731573778.775702</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1106,11 +1106,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'content-length': '795', 'date': 'Mon, 07 Oct 2024 08:52:45 GMT', 'server': 'LiteSpeed', 'location': 'https://www.halifleks.com/', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'content-length': '795', 'date': 'Thu, 14 Nov 2024 08:42:09 GMT', 'server': 'LiteSpeed', 'location': 'https://www.halifleks.com/', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.0001421422958374023</v>
+        <v>6.999969482421875e-06</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>200</v>
       </c>
       <c r="E7" t="n">
-        <v>1728291230.367131</v>
+        <v>1731573782.504155</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1233,11 +1233,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=59d4ff2466d11c21b91a2cf7ecc547f4; expires=Mon, 07-Oct-2024 09:52:44 GMT; Max-Age=3600; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=fE33qpYaqGDq5XVJ; expires=Mon, 07-Oct-2024 09:52:44 GMT; Max-Age=3600; path=/; domain=www.camihalicisi.com; secure; HttpOnly'), ('set-cookie', 'store=default; expires=Tue, 07-Oct-2025 08:52:44 GMT; Max-Age=31536000; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Mon, 07 Oct 2024 08:52:44 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=faf8bf81fce76ece9e51c63addd2c7a9; expires=Thu, 14-Nov-2024 09:42:07 GMT; Max-Age=3600; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=6X5K3cdRX9sSBqxn; expires=Thu, 14-Nov-2024 09:42:07 GMT; Max-Age=3600; path=/; domain=www.camihalicisi.com; secure; HttpOnly'), ('set-cookie', 'store=default; expires=Fri, 14-Nov-2025 08:42:08 GMT; Max-Age=31536000; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.camihalicisi.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('content-length', '10810'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:08 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.0001592025756835938</v>
+        <v>6.852531433105469e-05</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>200</v>
       </c>
       <c r="E8" t="n">
-        <v>1728291233.848748</v>
+        <v>1731573785.08745</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1360,11 +1360,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:27:57 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '184', 'date': 'Mon, 07 Oct 2024 08:52:45 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:27:57 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '184', 'date': 'Thu, 14 Nov 2024 08:42:07 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3.596019744873047e-05</v>
+        <v>3.606081008911133e-05</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>200</v>
       </c>
       <c r="E9" t="n">
-        <v>1728291237.192101</v>
+        <v>1731573787.711121</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:28:49 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '192', 'date': 'Mon, 07 Oct 2024 08:52:44 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:28:49 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '192', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.0001812822818756103</v>
+        <v>2.978515625e-05</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>200</v>
       </c>
       <c r="E10" t="n">
-        <v>1728291240.32472</v>
+        <v>1731573790.455734</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1614,11 +1614,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:28:10 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '186', 'date': 'Mon, 07 Oct 2024 08:52:44 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Sat, 21 Apr 2018 07:28:10 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '186', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4.16107177734375e-05</v>
+        <v>8.402228355407715e-05</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>200</v>
       </c>
       <c r="E11" t="n">
-        <v>1728291245.266752</v>
+        <v>1731573792.998335</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,11 +1741,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/5.6.40', 'content-type': 'text/html; charset=UTF-8', 'cache-control': 'no-store, no-cache, must-revalidate, post-check=0, pre-check=0', 'pragma': 'no-cache', 'x-frame-options': 'SAMEORIGIN', 'bubble-fpc': '3.5.1', 'transfer-encoding': 'chunked', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Mon, 07 Oct 2024 08:52:44 GMT', 'server': 'LiteSpeed', 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/5.6.40', 'content-type': 'text/html; charset=UTF-8', 'cache-control': 'no-store, no-cache, must-revalidate, post-check=0, pre-check=0', 'pragma': 'no-cache', 'x-frame-options': 'SAMEORIGIN', 'bubble-fpc': '3.5.1', 'transfer-encoding': 'chunked', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Thu, 14 Nov 2024 08:42:07 GMT', 'server': 'LiteSpeed', 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8.119058609008789e-05</v>
+        <v>8.353424072265625e-05</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>200</v>
       </c>
       <c r="E12" t="n">
-        <v>1728291248.292364</v>
+        <v>1731573795.810474</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1868,11 +1868,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Mon, 07 May 2018 08:09:28 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '186', 'date': 'Mon, 07 Oct 2024 08:52:45 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Mon, 07 May 2018 08:09:28 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '186', 'date': 'Thu, 14 Nov 2024 08:42:14 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.000160405158996582</v>
+        <v>8.009672164916992e-06</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1974,19 +1974,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>104.247.168.115</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E13" t="n">
-        <v>1726570681.264986</v>
+        <v>1731573798.913559</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1995,11 +1995,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/8.1.30'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.carpetsbook.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.carpetsbook.com/wp-json/wp/v2/pages/84&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.carpetsbook.com/&gt;; rel=shortlink'), ('etag', '"33499-1731510793;br"'), ('x-litespeed-cache', 'hit'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:13 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.106570243835449e-05</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>1156euct7.guzel.net.tr</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2101,19 +2101,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>45.84.190.3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E14" t="n">
-        <v>1726570682.465205</v>
+        <v>1731573800.51743</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2122,11 +2122,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.2.34', 'content-type': 'text/html; charset=UTF-8', 'content-length': '402', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Thu, 14 Nov 2024 08:42:07 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>7.924318313598633e-05</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2146,17 +2146,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>3sazof9.guzel.net.tr</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir Province</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>38.4127,27.1384</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>35210</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>38.4127</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>27.1384</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2228,19 +2228,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>45.84.190.3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" t="n">
-        <v>1726570685.927641</v>
+        <v>1731573803.336681</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2249,11 +2249,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'cache-control': 'public, max-age=0', 'expires': 'Thu, 14 Nov 2024 08:42:07 GMT', 'content-type': 'text/html; charset=UTF-8', 'last-modified': 'Wed, 13 Nov 2024 23:18:22 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'gzip', 'vary': 'Accept-Encoding,User-Agent,Accept-Encoding', 'content-length': '14046', 'date': 'Thu, 14 Nov 2024 08:42:07 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1.553845405578613e-05</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2273,17 +2273,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>3sazof9.guzel.net.tr</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir Province</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2293,17 +2293,17 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>38.4127,27.1384</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>35210</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>38.4127</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>27.1384</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2355,19 +2355,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E16" t="n">
-        <v>1726570688.278934</v>
+        <v>1731573806.642308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2376,41 +2376,41 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'wp_woocommerce_session_df8681de75e7e26f420ad8df31ba09c3=t_dc527d2a012a84626c8a5bf598abb9%7C%7C1731746532%7C%7C1731742932%7C%7C637aaa30df0cf45748d4bd65de359db9; expires=Sat, 16-Nov-2024 08:42:12 GMT; Max-Age=172799; path=/; secure; HttpOnly'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.confettihalilari.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.confettihalilari.com/wp-json/wp/v2/pages/554&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.confettihalilari.com/&gt;; rel=shortlink'), ('x-litespeed-cache-control', 'public,max-age=604800'), ('x-litespeed-tag', '64d_HTTP.200,64d_front,64d_URL.6666cd76f96956469e7be39d750cc7d9,64d_F,64d_Po.554,64d_PGS,64d_'), ('etag', '"950719-1731573733;br"'), ('x-litespeed-cache', 'miss'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding'), ('date', 'Thu, 14 Nov 2024 08:42:13 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>8.005857467651367e-06</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>www.turkfleks.halivizyon.com</t>
+          <t>turkfleks.com</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>45539.03967592592</v>
+        <v>45597.41471064815</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>45629.03966435185</v>
+        <v>45687.41469907408</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2420,17 +2420,17 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2482,19 +2482,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E17" t="n">
-        <v>1726570689.440717</v>
+        <v>1731573808.671479</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2503,11 +2503,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'date': 'Thu, 14 Nov 2024 08:42:10 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3.152585029602051e-05</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2527,17 +2527,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2547,17 +2547,17 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2609,19 +2609,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E18" t="n">
-        <v>1726570690.741832</v>
+        <v>1731573810.38482</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2630,11 +2630,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3.994226455688477e-06</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2674,17 +2674,17 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E19" t="n">
-        <v>1726570692.101478</v>
+        <v>1731573811.701487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2757,11 +2757,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'date': 'Thu, 14 Nov 2024 08:42:12 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>4.970741271972656e-05</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2781,17 +2781,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E20" t="n">
-        <v>1726570693.269701</v>
+        <v>1731573813.330356</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '324', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Thu, 14 Nov 2024 08:42:12 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2908,17 +2908,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2928,17 +2928,17 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2990,19 +2990,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E21" t="n">
-        <v>1726570694.711801</v>
+        <v>1731573814.942927</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3011,11 +3011,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '324', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Thu, 14 Nov 2024 08:42:11 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4.353570938110352e-05</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -3035,17 +3035,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3055,17 +3055,17 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3117,19 +3117,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E22" t="n">
-        <v>1726570695.860456</v>
+        <v>1731573816.720118</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3138,11 +3138,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 15 Jun 2017 10:48:16 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '291', 'date': 'Thu, 14 Nov 2024 08:42:12 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3.213667869567871e-05</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3162,17 +3162,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3182,17 +3182,17 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3244,19 +3244,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E23" t="n">
-        <v>1726570698.370225</v>
+        <v>1731573820.416271</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3265,41 +3265,41 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.dinarsuhalilari.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.dinarsuhalilari.com/wp-json/wp/v2/pages/544&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.dinarsuhalilari.com/&gt;; rel=shortlink'), ('etag', '"946530-1731549753;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding'), ('content-length', '20140'), ('date', 'Thu, 14 Nov 2024 08:42:09 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>5.652451515197754e-05</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>*.dinarsuhalilari.com</t>
+          <t>*.turkflexhalilari.com</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>45539.53934027778</v>
+        <v>45598.03903935185</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>45629.5393287037</v>
+        <v>45688.03902777778</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3309,17 +3309,17 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3371,19 +3371,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.180.102</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" t="n">
-        <v>1726570700.685099</v>
+        <v>1731573822.986021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=bce444a3bd2a6ee5c87f1619cb8bb9cf; expires=Thu, 14-Nov-2024 09:42:13 GMT; Max-Age=3600; path=/; domain=www.duvardanduvara.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=FMOr3oOrtBwCkzNx; expires=Thu, 14-Nov-2024 09:42:13 GMT; Max-Age=3600; path=/; domain=www.duvardanduvara.com; secure; HttpOnly'), ('set-cookie', 'store=default; expires=Fri, 14-Nov-2025 08:42:13 GMT; Max-Age=31536000; path=/; domain=www.duvardanduvara.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.duvardanduvara.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:13 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3.245139122009277e-05</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3409,14 +3409,14 @@
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>45532.23069444444</v>
+        <v>45590.51363425926</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>45622.23068287037</v>
+        <v>45680.51362268518</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>102w8oqex.guzel.net.tr</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3498,19 +3498,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>104.247.168.115</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E25" t="n">
-        <v>1726570702.744654</v>
+        <v>1731573825.80424</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3519,11 +3519,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Tue, 19 Apr 2022 11:39:44 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '5967', 'date': 'Thu, 14 Nov 2024 08:42:18 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3.559160232543946e-05</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>1156euct7.guzel.net.tr</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3625,19 +3625,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>45.84.190.3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E26" t="n">
-        <v>1726570705.812158</v>
+        <v>1731573828.325365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3646,11 +3646,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.ehalici.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.ehalici.com/wp-json/wp/v2/pages/466&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.ehalici.com/&gt;; rel=shortlink'), ('etag', '"553713-1731491271;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('content-length', '24652'), ('date', 'Thu, 14 Nov 2024 08:42:13 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3.199958801269531e-05</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3670,17 +3670,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>3sazof9.guzel.net.tr</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir Province</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>38.4127,27.1384</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>35210</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>38.4127</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>27.1384</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3752,19 +3752,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>104.247.167.211</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E27" t="n">
-        <v>1726570708.888397</v>
+        <v>1731573832.678336</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3773,11 +3773,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.emanhali.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.emanhali.com/wp-json/wp/v2/pages/7682&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.emanhali.com/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:15 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3.036236763000488e-05</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3786,18 +3786,18 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>45527.5362037037</v>
+        <v>45586.03626157407</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>45617.53619212963</v>
+        <v>45676.03625</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>211hyd4no.guzel.net.tr</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3879,19 +3879,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.183.35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E28" t="n">
-        <v>1726570711.048334</v>
+        <v>1731573835.742668</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3900,11 +3900,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/8.1.30'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.emanzemin.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.emanzemin.com/wp-json/wp/v2/pages/11&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.emanzemin.com/&gt;; rel=shortlink'), ('etag', '"54387-1731564820;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('content-length', '42336'), ('date', 'Thu, 14 Nov 2024 08:42:15 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>8.030891418457031e-05</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3913,18 +3913,18 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>45551.60317129629</v>
+        <v>45609.68944444445</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>45641.60315972222</v>
+        <v>45699.68943287037</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>35rby11p.guzel.net.tr</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4006,19 +4006,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.180.102</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E29" t="n">
-        <v>1726570712.262018</v>
+        <v>1731573837.918775</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4027,11 +4027,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'cache-control': 'private, no-cache, no-store, must-revalidate, max-age=0', 'pragma': 'no-cache', 'content-type': 'text/html', 'content-length': '1238', 'date': 'Thu, 14 Nov 2024 08:42:14 GMT', 'server': 'LiteSpeed', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2.925848960876465e-05</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>102w8oqex.guzel.net.tr</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4133,19 +4133,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.180.102</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E30" t="n">
-        <v>1726570715.508468</v>
+        <v>1731573841.134508</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4154,11 +4154,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.evaminder.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.evaminder.com/wp-json/wp/v2/pages/553&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.evaminder.com/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:14 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2.800512313842774e-05</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4167,18 +4167,18 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>45496.83490740741</v>
+        <v>45587.35037037037</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>45586.83489583333</v>
+        <v>45677.3503587963</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>102w8oqex.guzel.net.tr</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4260,19 +4260,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E31" t="n">
-        <v>1726570716.560016</v>
+        <v>1731573842.551338</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4281,11 +4281,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2.801394462585449e-05</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4305,17 +4305,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4325,17 +4325,17 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4387,122 +4387,122 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>91.108.98.254</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>301</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1731573845.965051</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>www.gursoyrealty.com_.png</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Headers({'server': 'hcdn', 'date': 'Thu, 14 Nov 2024 08:42:17 GMT', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'connection': 'keep-alive', 'x-powered-by': 'PHP/8.1.27', 'x-redirect-by': 'WordPress', 'location': 'https://gursoyrealty.com/', 'cache-control': 'public, max-age=604800', 'expires': 'Thu, 21 Nov 2024 08:42:17 GMT', 'x-litespeed-cache': 'miss', 'platform': 'hostinger', 'panel': 'hpanel', 'content-security-policy': 'upgrade-insecure-requests', 'alt-svc': 'h3=":443"; ma=86400', 'x-hcdn-request-id': '3f8ada209d420b2e5e40ca77c2102d78-srv-edge4', 'x-hcdn-cache-status': 'MISS', 'x-hcdn-upstream-rt': '1.352'})</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>8.810591697692871e-05</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>gursoyrealty.com</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>['US', "Let's Encrypt", 'R11']</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>45599.51125</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>45689.51123842593</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1726570719.760163</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>www.gursoyrealty.com_.png</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>gursoyrealty.com</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>45539.54785879629</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>45629.54784722222</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>130.107.146.159.srv.turk.net</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Meppel</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Drenthe</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>52.6958,6.1944</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS47583 Hostinger International Limited</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Europe/Istanbul</t>
+          <t>Europe/Amsterdam</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>52.6958</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>6.1944</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/NL.svg</t>
         </is>
       </c>
     </row>
@@ -4514,19 +4514,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.183.211</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E33" t="n">
-        <v>1726570721.397102</v>
+        <v>1731573849.165143</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4535,11 +4535,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'set-cookie': 'PHPSESSID=72bc03104e12611579dca3e5a9d726b4; path=/; HttpOnly; secure', 'expires': 'Thu, 19 Nov 1981 08:52:00 GMT', 'cache-control': 'no-store, no-cache, must-revalidate', 'pragma': 'no-cache', 'content-type': 'text/html; charset=UTF-8', 'transfer-encoding': 'chunked', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Thu, 14 Nov 2024 08:42:14 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>4.008769989013672e-06</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -4548,18 +4548,18 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
-        <v>45547.04143518519</v>
+        <v>45605.19958333333</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>45637.04142361111</v>
+        <v>45695.19957175926</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>211km5vaq.guzel.net.tr</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4641,19 +4641,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E34" t="n">
-        <v>1726570722.737031</v>
+        <v>1731573851.264546</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4662,11 +4662,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 15 Jun 2017 10:57:31 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '296', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2.827024459838867e-05</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -4686,17 +4686,17 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4768,19 +4768,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E35" t="n">
-        <v>1726570723.904348</v>
+        <v>1731573853.117188</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4789,11 +4789,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Mon, 03 Jul 2017 12:40:28 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '281', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>3.192234039306641e-05</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -4813,17 +4813,17 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4833,17 +4833,17 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4895,19 +4895,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>104.247.167.211</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E36" t="n">
-        <v>1726570725.832482</v>
+        <v>1731573856.156801</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4916,15 +4916,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'cache-control': 'no-store, no-cache, must-revalidate, post-check=0, pre-check=0', 'pragma': 'no-cache', 'x-frame-options': 'SAMEORIGIN', 'bubble-fpc': '3.5.1', 'content-length': '13277', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Thu, 14 Nov 2024 08:42:14 GMT', 'server': 'LiteSpeed', 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>2.202463150024414e-05</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>cpcontacts.halifleks.com</t>
+          <t>halifleks.com</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4933,14 +4933,14 @@
         </is>
       </c>
       <c r="K36" s="2" t="n">
-        <v>45527.41172453704</v>
+        <v>45585.4112037037</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>45617.41171296296</v>
+        <v>45675.41119212963</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>211hyd4no.guzel.net.tr</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -5022,19 +5022,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>45.84.190.3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E37" t="n">
-        <v>1726570726.982428</v>
+        <v>1731573858.258408</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5043,11 +5043,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.2.34', 'content-type': 'text/html; charset=UTF-8', 'content-length': '404', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'date': 'Thu, 14 Nov 2024 08:42:14 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>6.241798400878907e-05</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -5067,17 +5067,17 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>3sazof9.guzel.net.tr</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir Province</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5087,17 +5087,17 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>38.4127,27.1384</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>35210</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>38.4127</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>27.1384</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5149,19 +5149,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>104.247.168.115</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E38" t="n">
-        <v>1726570728.923438</v>
+        <v>1731573860.510963</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5170,11 +5170,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/8.1.30'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.haliutubandi.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.haliutubandi.com/wp-json/wp/v2/pages/1263&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.haliutubandi.com/&gt;; rel=shortlink'), ('x-litespeed-cache-control', 'public,max-age=604800'), ('x-litespeed-tag', '13a_HTTP.200,13a_front,13a_URL.6666cd76f96956469e7be39d750cc7d9,13a_F,13a_Po.1263,13a_PGS,13a_'), ('etag', '"34674-1731573745;br"'), ('x-litespeed-cache', 'miss'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:25 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2.842855453491211e-05</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>1156euct7.guzel.net.tr</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -5276,19 +5276,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E39" t="n">
-        <v>1726570731.075528</v>
+        <v>1731573862.798936</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5297,41 +5297,41 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.halivizyon.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.halivizyon.com/wp-json/wp/v2/pages/97&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.halivizyon.com/&gt;; rel=shortlink'), ('etag', '"950490-1731572810;br"'), ('x-litespeed-cache', 'hit'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding'), ('date', 'Thu, 14 Nov 2024 08:42:13 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>4.110288619995117e-05</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>*.dinarsuhalilari.com</t>
+          <t>*.turkflexhalilari.com</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K39" s="2" t="n">
-        <v>45539.53934027778</v>
+        <v>45598.03903935185</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>45629.5393287037</v>
+        <v>45688.03902777778</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5403,19 +5403,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>104.247.168.115</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E40" t="n">
-        <v>1726570734.946724</v>
+        <v>1731573866.693176</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5424,11 +5424,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/8.1.30'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.haliyapistirici.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.haliyapistirici.com/wp-json/wp/v2/pages/1263&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.haliyapistirici.com/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:24 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.0001620175838470459</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>1156euct7.guzel.net.tr</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5530,19 +5530,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>51.195.87.128</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E41" t="n">
-        <v>1726570737.055303</v>
+        <v>1731573868.796962</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5551,11 +5551,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=0ce0422b6745013c76a284f291a034fb; expires=Thu, 14-Nov-2024 09:42:15 GMT; Max-Age=3600; path=/; domain=www.hediyepaspas.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=PopXTO8jIhAz2q19; expires=Thu, 14-Nov-2024 09:42:15 GMT; Max-Age=3600; path=/; domain=www.hediyepaspas.com; secure; HttpOnly'), ('set-cookie', 'store=default; expires=Fri, 14-Nov-2025 08:42:15 GMT; Max-Age=31536000; path=/; domain=www.hediyepaspas.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.hediyepaspas.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:15 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>3.999590873718262e-05</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -5575,77 +5575,77 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>ip128.ip-51-195-87.eu</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>50.1155,8.6842</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS16276 OVH SAS</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>60306</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Europe/Istanbul</t>
+          <t>Europe/Berlin</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>50.1155</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>8.6842</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
         </is>
       </c>
     </row>
@@ -5657,19 +5657,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.180.162</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E42" t="n">
-        <v>1726570739.982847</v>
+        <v>1731573872.11854</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5678,11 +5678,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/5.6.40', 'content-type': 'text/html; charset=UTF-8', 'cache-control': 'no-store, no-cache, must-revalidate, post-check=0, pre-check=0', 'pragma': 'no-cache', 'x-frame-options': 'SAMEORIGIN', 'bubble-fpc': '3.5.1', 'content-length': '15225', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Thu, 14 Nov 2024 08:42:14 GMT', 'server': 'LiteSpeed', 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>3.200912475585938e-05</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>162p94xyd.guzel.net.tr</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5784,19 +5784,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.180.102</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E43" t="n">
-        <v>1726570741.194142</v>
+        <v>1731573873.901251</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5805,11 +5805,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'cache-control': 'private, no-cache, no-store, must-revalidate, max-age=0', 'pragma': 'no-cache', 'content-type': 'text/html', 'content-length': '1238', 'date': 'Thu, 14 Nov 2024 08:42:14 GMT', 'server': 'LiteSpeed', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>8.008718490600586e-06</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -5818,18 +5818,18 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>45529.71115740741</v>
+        <v>45587.85824074074</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>45619.71114583333</v>
+        <v>45677.85822916667</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>102w8oqex.guzel.net.tr</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5911,19 +5911,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.180.102</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E44" t="n">
-        <v>1726570743.040118</v>
+        <v>1731573876.791786</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5932,11 +5932,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'cache-control': 'no-store, no-cache, must-revalidate, post-check=0, pre-check=0', 'pragma': 'no-cache', 'x-frame-options': 'SAMEORIGIN', 'bubble-fpc': '3.5.1', 'transfer-encoding': 'chunked', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Thu, 14 Nov 2024 08:42:14 GMT', 'server': 'LiteSpeed', 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2.846193313598633e-05</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>102w8oqex.guzel.net.tr</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -6038,19 +6038,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>51.195.87.128</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E45" t="n">
-        <v>1726570744.876788</v>
+        <v>1731573879.291891</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6059,11 +6059,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'cache-control': 'public', 'expires': 'Thu, 14 Nov 2024 08:42:15 GMT', 'content-type': 'text/html', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'content-length': '15631', 'date': 'Thu, 14 Nov 2024 08:42:15 GMT', 'server': 'LiteSpeed', 'x-speedycache-source': 'Server', 'cache-tag': 'www.karehalilar.com', 'cdn-cache-control': 'max-age=1296000', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>3.61950397491455e-05</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -6072,88 +6072,88 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>45520.31297453704</v>
+        <v>45578.38789351852</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>45610.31296296296</v>
+        <v>45668.38788194444</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>ip128.ip-51-195-87.eu</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>50.1155,8.6842</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS16276 OVH SAS</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>60306</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Europe/Istanbul</t>
+          <t>Europe/Berlin</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>50.1155</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>8.6842</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
         </is>
       </c>
     </row>
@@ -6165,19 +6165,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>51.195.87.128</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="E46" t="n">
-        <v>1726570748.58509</v>
+        <v>1731573882.969414</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6186,11 +6186,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'content-length': '795', 'date': 'Thu, 14 Nov 2024 08:42:15 GMT', 'server': 'LiteSpeed', 'location': 'https://www.karohalicim.com/tr/', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>3.198361396789551e-05</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -6203,84 +6203,84 @@
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>45520.31351851852</v>
+        <v>45578.38844907407</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>45610.31350694445</v>
+        <v>45668.3884375</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>ip128.ip-51-195-87.eu</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>50.1155,8.6842</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS16276 OVH SAS</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>60306</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Europe/Istanbul</t>
+          <t>Europe/Berlin</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>50.1155</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>8.6842</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
         </is>
       </c>
     </row>
@@ -6292,19 +6292,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.183.211</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E47" t="n">
-        <v>1726570750.707183</v>
+        <v>1731573886.080022</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6313,11 +6313,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.karokaucukzemin.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.karokaucukzemin.com/wp-json/wp/v2/pages/633&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.karokaucukzemin.com/&gt;; rel=shortlink'), ('etag', '"472-1731551914;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('content-length', '19430'), ('date', 'Thu, 14 Nov 2024 08:42:14 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>2.792024612426758e-05</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>211km5vaq.guzel.net.tr</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6419,19 +6419,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E48" t="n">
-        <v>1726570751.92368</v>
+        <v>1731573892.278341</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6440,11 +6440,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.kivircikhali.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.kivircikhali.com/wp-json/wp/v2/pages/7&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.kivircikhali.com/&gt;; rel=shortlink'), ('x-litespeed-cache-control', 'public,max-age=604800'), ('x-litespeed-tag', '048_HTTP.200,048_front,048_URL.6666cd76f96956469e7be39d750cc7d9,048_F,048_Po.7,048_PGS,048_'), ('etag', '"950722-1731573737;br"'), ('x-litespeed-cache', 'miss'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding'), ('date', 'Thu, 14 Nov 2024 08:42:17 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>3.832697868347168e-05</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6546,19 +6546,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.183.211</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E49" t="n">
-        <v>1726570753.645363</v>
+        <v>1731573895.112481</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6567,11 +6567,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'set-cookie': 'PHPSESSID=0d2231ff23aa07e05fb03224d17693a6; path=/; HttpOnly; secure', 'expires': 'Thu, 19 Nov 1981 08:52:00 GMT', 'cache-control': 'no-store, no-cache, must-revalidate', 'pragma': 'no-cache', 'content-type': 'text/html; charset=UTF-8', 'content-length': '11355', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Thu, 14 Nov 2024 08:42:14 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>6.073713302612305e-06</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -6580,18 +6580,18 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>45546.21954861111</v>
+        <v>45604.63405092592</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>45636.21953703704</v>
+        <v>45694.63403935185</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>211km5vaq.guzel.net.tr</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -6673,19 +6673,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.183.211</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E50" t="n">
-        <v>1726570755.372984</v>
+        <v>1731573897.642758</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6694,11 +6694,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'set-cookie': 'PHPSESSID=f0118971062ddb03b6ac5320c5d385d8; path=/; HttpOnly; secure', 'expires': 'Thu, 19 Nov 1981 08:52:00 GMT', 'cache-control': 'no-store, no-cache, must-revalidate', 'pragma': 'no-cache', 'content-type': 'text/html; charset=UTF-8', 'content-length': '11532', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Thu, 14 Nov 2024 08:42:14 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>2.808427810668945e-05</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -6711,14 +6711,14 @@
         </is>
       </c>
       <c r="K50" s="2" t="n">
-        <v>45516.12018518519</v>
+        <v>45574.23320601852</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>45606.12017361111</v>
+        <v>45664.23319444444</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>211km5vaq.guzel.net.tr</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -6800,19 +6800,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.183.211</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E51" t="n">
-        <v>1726570757.506343</v>
+        <v>1731573900.678256</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6821,11 +6821,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.mescithalisi.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.mescithalisi.com/wp-json/wp/v2/pages/6019131&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.mescithalisi.com/&gt;; rel=shortlink'), ('etag', '"468-1731546585;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('content-length', '24709'), ('date', 'Thu, 14 Nov 2024 08:42:14 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>3.199958801269531e-05</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -6838,14 +6838,14 @@
         </is>
       </c>
       <c r="K51" s="2" t="n">
-        <v>45541.93518518518</v>
+        <v>45600.00969907407</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>45631.93517361111</v>
+        <v>45690.0096875</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>211km5vaq.guzel.net.tr</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -6927,19 +6927,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.183.211</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E52" t="n">
-        <v>1726570759.537582</v>
+        <v>1731573903.928761</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6948,11 +6948,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.mineflocu.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.mineflocu.com/wp-json/wp/v2/pages/7366&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.mineflocu.com/&gt;; rel=shortlink'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:16 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>8.027410507202149e-05</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -6961,18 +6961,18 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K52" s="2" t="n">
-        <v>45518.39760416667</v>
+        <v>45576.61986111111</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>45608.39759259259</v>
+        <v>45666.61984953703</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>211km5vaq.guzel.net.tr</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -7054,19 +7054,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>185.106.210.162</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E53" t="n">
-        <v>1726570761.513508</v>
+        <v>1731573910.376775</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7075,11 +7075,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/8.2.24'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.myfloor.com.tr/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.myfloor.com.tr/wp-json/wp/v2/pages/7105&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.myfloor.com.tr/&gt;; rel=shortlink'), ('server-timing', 'wp-before-template;dur=1436.45'), ('etag', '"11453-1731572034;br"'), ('x-litespeed-cache', 'hit'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:14 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>3.153491020202637e-05</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -7088,28 +7088,28 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K53" s="2" t="n">
-        <v>45520.65879629629</v>
+        <v>45578.62898148148</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>45610.65878472223</v>
+        <v>45668.6289699074</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>162uzpsk0.guzel.net.tr</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir Province</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7119,17 +7119,17 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>38.4127,27.1384</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>35210</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>38.4127</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>27.1384</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7181,19 +7181,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>51.195.87.128</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E54" t="n">
-        <v>1726570763.41641</v>
+        <v>1731573912.484244</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7202,11 +7202,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=d2b06d2eb5af93b367d94028fbd6a337; expires=Thu, 14-Nov-2024 09:42:15 GMT; Max-Age=3600; path=/; domain=www.paspasfabrikasi.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=ScKVQyGTt5XgSaeu; expires=Thu, 14-Nov-2024 09:42:15 GMT; Max-Age=3600; path=/; domain=www.paspasfabrikasi.com; secure; HttpOnly'), ('set-cookie', 'store=default; expires=Fri, 14-Nov-2025 08:42:15 GMT; Max-Age=31536000; path=/; domain=www.paspasfabrikasi.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.paspasfabrikasi.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:15 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2.803230285644531e-05</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -7219,84 +7219,84 @@
         </is>
       </c>
       <c r="K54" s="2" t="n">
-        <v>45516.5600462963</v>
+        <v>45574.59244212963</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>45606.56003472222</v>
+        <v>45664.59243055555</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>ip128.ip-51-195-87.eu</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>50.1155,8.6842</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS16276 OVH SAS</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>60306</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Europe/Istanbul</t>
+          <t>Europe/Berlin</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>50.1155</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>8.6842</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
         </is>
       </c>
     </row>
@@ -7308,19 +7308,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E55" t="n">
-        <v>1726570764.78545</v>
+        <v>1731573914.269105</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7329,11 +7329,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 15 Jun 2017 11:07:34 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '291', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>7.993507385253906e-05</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -7353,17 +7353,17 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7435,19 +7435,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E56" t="n">
-        <v>1726570766.230831</v>
+        <v>1731573916.181405</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7456,11 +7456,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 15 Jun 2017 11:08:04 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '291', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>3.210210800170898e-05</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -7480,17 +7480,17 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7500,17 +7500,17 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7562,19 +7562,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E57" t="n">
-        <v>1726570767.621725</v>
+        <v>1731573917.832688</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7583,41 +7583,41 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Thu, 15 Jun 2017 11:09:18 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '299', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>2.80001163482666e-05</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>www.protokolhalilari.halivizyon.com</t>
+          <t>*.protokolhalilari.com</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>45511.41355324074</v>
+        <v>45572.53822916667</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>45601.41354166667</v>
+        <v>45662.53821759259</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7627,17 +7627,17 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -7667,12 +7667,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7718,23 +7718,23 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>www.turkfleks.halivizyon.com</t>
+          <t>turkfleks.com</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>45539.03967592592</v>
+        <v>45597.41471064815</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>45629.03966435185</v>
+        <v>45687.41469907408</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>105.58.223.31.srv.turk.net</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -7816,19 +7816,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>185.106.210.162</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E59" t="n">
-        <v>1726570774.456992</v>
+        <v>1731573920.296235</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7837,11 +7837,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/8.2.24', 'set-cookie': 'PHPSESSID=nhgbcqdosvqih54nri2kus37g4; expires=Thu, 14 Nov 2024 09:42:14 GMT; Max-Age=3600; path=/; domain=www.stepmat.com.tr; secure; HttpOnly; SameSite=Lax', 'pragma': 'no-cache', 'cache-control': 'max-age=0, must-revalidate, no-cache, no-store', 'expires': 'Mon, 13 Nov 2023 13:40:07 GMT', 'content-security-policy-report-only': "font-src data: 'self' 'unsafe-inline'; form-action geostag.cardinalcommerce.com geo.cardinalcommerce.com 1eafstag.cardinalcommerce.com 1eaf.cardinalcommerce.com centinelapistag.cardinalcommerce.com centinelapi.cardinalcommerce.com pilot-payflowlink.paypal.com www.paypal.com www.sandbox.paypal.com *.cardinalcommerce.com *.paypal.com 3ds-secure.cardcomplete.com www.clicksafe.lloydstsb.com pay.activa-card.com *.wirecard.com acs.sia.eu *.touchtechpayments.com www.securesuite.co.uk rsa3dsauth.com *.monzo.com *.arcot.com *.wlp-acs.com * 'self' 'unsafe-inline'; frame-ancestors 'self'; frame-src fast.amc.demdex.net *.adobe.com bid.g.doubleclick.net *.youtube.com *.youtube-nocookie.com geostag.cardinalcommerce.com geo.cardinalcommerce.com 1eafstag.cardinalcommerce.com 1eaf.cardinalcommerce.com centinelapistag.cardinalcommerce.com centinelapi.cardinalcommerce.com www.paypal.com www.sandbox.paypal.com pilot-payflowlink.paypal.com player.vimeo.com https://www.google.com/recaptcha/ c.paypal.com checkout.paypal.com assets.braintreegateway.com pay.google.com *.cardinalcommerce.com *.paypal.com * 'self' 'unsafe-inline'; img-src assets.adobedtm.com amcglobal.sc.omtrdc.net dpm.demdex.net cm.everesttech.net *.adobe.com widgets.magentocommerce.com data: www.googleadservices.com www.google-analytics.com googleads.g.doubleclick.net www.google.com bid.g.doubleclick.net analytics.google.com www.googletagmanager.com *.ftcdn.net *.behance.net t.paypal.com www.paypal.com www.paypalobjects.com fpdbs.paypal.com fpdbs.sandbox.paypal.com *.vimeocdn.com i.ytimg.com *.youtube.com validator.swagger.io www.sandbox.paypal.com b.stats.paypal.com dub.stats.paypal.com assets.braintreegateway.com c.paypal.com checkout.paypal.com *.paypal.com data: 'self' 'unsafe-inline'; script-src assets.adobedtm.com *.adobe.com www.googleadservices.com www.google-analytics.com googleads.g.doubleclick.net analytics.google.com www.googletagmanager.com *.newrelic.com *.nr-data.net geostag.cardinalcommerce.com 1eafstag.cardinalcommerce.com geoapi.cardinalcommerce.com 1eafapi.cardinalcommerce.com songbird.cardinalcommerce.com includestest.ccdc02.com www.paypal.com www.sandbox.paypal.com www.paypalobjects.com t.paypal.com s.ytimg.com www.googleapis.com vimeo.com www.vimeo.com *.vimeocdn.com *.youtube.com https://www.gstatic.com/recaptcha/ https://www.google.com/recaptcha/ js.braintreegateway.com assets.braintreegateway.com c.paypal.com pay.google.com api.braintreegateway.com api.sandbox.braintreegateway.com client-analytics.braintreegateway.com client-analytics.sandbox.braintreegateway.com *.paypal.com songbirdstag.cardinalcommerce.com 'self' 'unsafe-inline' 'unsafe-eval'; style-src *.adobe.com unsafe-inline assets.braintreegateway.com 'self' 'unsafe-inline'; object-src 'self' 'unsafe-inline'; media-src *.adobe.com 'self' 'unsafe-inline'; manifest-src 'self' 'unsafe-inline'; connect-src dpm.demdex.net amcglobal.sc.omtrdc.net www.google-analytics.com www.googleadservices.com analytics.google.com www.googletagmanager.com *.newrelic.com *.nr-data.net vimeo.com geostag.cardinalcommerce.com geo.cardinalcommerce.com 1eafstag.cardinalcommerce.com 1eaf.cardinalcommerce.com centinelapistag.cardinalcommerce.com centinelapi.cardinalcommerce.com www.sandbox.paypal.com www.paypalobjects.com www.paypal.com pilot-payflowlink.paypal.com api.braintreegateway.com api.sandbox.braintreegateway.com client-analytics.braintreegateway.com client-analytics.sandbox.braintreegateway.com *.braintree-api.com *.paypal.com *.cardinalcommerce.com *.google.com google.com 'self' 'unsafe-inline'; child-src assets.braintreegateway.com c.paypal.com *.paypal.com http: https: blob: 'self' 'unsafe-inline'; default-src 'self' 'unsafe-inline' 'unsafe-eval'; base-uri 'self' 'unsafe-inline';", 'x-content-type-options': 'nosniff', 'x-xss-protection': '1; mode=block', 'x-frame-options': 'SAMEORIGIN', 'content-type': 'text/html; charset=UTF-8', 'transfer-encoding': 'chunked', 'content-encoding': 'br', 'vary': 'Accept-Encoding,User-Agent', 'date': 'Thu, 14 Nov 2024 08:42:14 GMT', 'server': 'LiteSpeed', 'x-ua-compatible': 'IE=edge', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>4.019737243652344e-06</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -7854,24 +7854,24 @@
         </is>
       </c>
       <c r="K59" s="2" t="n">
-        <v>45520.6583912037</v>
+        <v>45578.6282175926</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>45610.65837962963</v>
+        <v>45668.62820601852</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>162uzpsk0.guzel.net.tr</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>İzmir Province</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7881,17 +7881,17 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>38.4127,27.1384</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>35210</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>38.4127</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>27.1384</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7943,19 +7943,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>104.247.168.115</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E60" t="n">
-        <v>1726570775.681856</v>
+        <v>1731573922.566457</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7964,31 +7964,31 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/8.1.30'), ('set-cookie', 'frontend=vgqnk2ee97jpc99og91vpi7mcm; expires=Thu, 14-Nov-2024 09:42:18 GMT; Max-Age=3600; path=/; domain=www.sunicimhali.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=8xlKe6EHqK0PESFn; expires=Thu, 14-Nov-2024 09:42:18 GMT; Max-Age=3600; path=/; domain=www.sunicimhali.com; secure; HttpOnly'), ('set-cookie', 'store=tr_tr; expires=Fri, 14-Nov-2025 08:42:19 GMT; Max-Age=31536000; path=/; domain=www.sunicimhali.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.sunicimhali.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:19 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>3.200745582580566e-05</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>cpcontacts.sunicimhali.com</t>
+          <t>sunicimhali.com</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R10']</t>
+          <t>['US', "Let's Encrypt", 'R11']</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>45572.19291666667</v>
+        <v>45598.52252314815</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>45662.19290509259</v>
+        <v>45688.52251157408</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>1156euct7.guzel.net.tr</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -8070,19 +8070,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E61" t="n">
-        <v>1726570776.964494</v>
+        <v>1731573924.316962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8091,11 +8091,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Tue, 02 Jul 2019 11:53:54 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '179', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>3.190350532531738e-05</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -8115,17 +8115,17 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -8135,17 +8135,17 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8197,19 +8197,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E62" t="n">
-        <v>1726570779.295804</v>
+        <v>1731573926.499754</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8218,11 +8218,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Tue, 02 Jul 2019 12:23:00 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '195', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>3.602480888366699e-05</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -8242,17 +8242,17 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8262,17 +8262,17 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8324,19 +8324,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>89.252.183.211</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E63" t="n">
-        <v>1726570781.074097</v>
+        <v>1731573928.907456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8345,11 +8345,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.tatamiminder.net/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.tatamiminder.net/wp-json/wp/v2/pages/553&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.tatamiminder.net/&gt;; rel=shortlink'), ('etag', '"386-1731408949;br"'), ('x-litespeed-cache', 'hit'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('content-length', '22059'), ('date', 'Thu, 14 Nov 2024 08:42:14 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.0002123045921325684</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -8362,14 +8362,14 @@
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>45518.39711805555</v>
+        <v>45576.61953703704</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>45608.39710648148</v>
+        <v>45666.61952546296</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>211km5vaq.guzel.net.tr</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8451,19 +8451,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E64" t="n">
-        <v>1726570782.631825</v>
+        <v>1731573931.581346</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8472,11 +8472,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'last-modified': 'Tue, 02 Jul 2019 12:29:08 GMT', 'accept-ranges': 'bytes', 'content-encoding': 'br', 'vary': 'Accept-Encoding', 'content-length': '195', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>8.000516891479492e-05</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -8496,17 +8496,17 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8578,19 +8578,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E65" t="n">
-        <v>1726570786.761294</v>
+        <v>1731573934.67969</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8599,41 +8599,41 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('content-type', 'text/html; charset=UTF-8'), ('link', '&lt;https://www.turkfleks.com/wp-json/&gt;; rel="https://api.w.org/"'), ('link', '&lt;https://www.turkfleks.com/wp-json/wp/v2/pages/875&gt;; rel="alternate"; title="JSON"; type="application/json"'), ('link', '&lt;https://www.turkfleks.com/&gt;; rel=shortlink'), ('etag', '"944941-1731535921;br"'), ('x-litespeed-cache', 'hit'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding'), ('date', 'Thu, 14 Nov 2024 08:42:13 GMT'), ('server', 'LiteSpeed'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>3.625249862670898e-05</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>www.turkfleks.halivizyon.com</t>
+          <t>turkfleks.com</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>45539.03967592592</v>
+        <v>45597.41471064815</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>45629.03966435185</v>
+        <v>45687.41469907408</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8643,17 +8643,17 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8705,19 +8705,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>31.192.212.112</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E66" t="n">
-        <v>1726570787.84602</v>
+        <v>1731573936.301405</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8726,11 +8726,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'x-powered-by': 'PHP/7.4.33', 'content-type': 'text/html; charset=UTF-8', 'content-length': '0', 'date': 'Thu, 14 Nov 2024 08:42:13 GMT', 'server': 'LiteSpeed', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>2.789735794067383e-05</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -8750,17 +8750,17 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>112zop6uj.guzel.net.tr</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Denizli</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8770,17 +8770,17 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>37.7742,29.0875</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS42846 GNET Internet Telekomunikasyon A.S.</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>37.7742</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>29.0875</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8832,19 +8832,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>51.195.87.128</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="E67" t="n">
-        <v>1726570791.510156</v>
+        <v>1731573939.974332</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8853,11 +8853,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers({'connection': 'Keep-Alive', 'keep-alive': 'timeout=5, max=100', 'content-type': 'text/html', 'content-length': '795', 'date': 'Thu, 14 Nov 2024 08:42:15 GMT', 'server': 'LiteSpeed', 'location': 'https://www.ucuzkarohalilar.com/tr/', 'vary': 'User-Agent', 'alt-svc': 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"'})</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.0001121513843536377</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -8866,88 +8866,88 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>['US', "Let's Encrypt", 'R11']</t>
+          <t>['US', "Let's Encrypt", 'R10']</t>
         </is>
       </c>
       <c r="K67" s="2" t="n">
-        <v>45520.31252314815</v>
+        <v>45578.38916666667</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>45610.31251157408</v>
+        <v>45668.38915509259</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>ip128.ip-51-195-87.eu</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>50.1155,8.6842</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS16276 OVH SAS</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>60306</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Europe/Istanbul</t>
+          <t>Europe/Berlin</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>50.1155</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>8.6842</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
         </is>
       </c>
     </row>
@@ -8959,19 +8959,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IP Not Found</t>
+          <t>51.195.87.128</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Up</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E68" t="n">
-        <v>1726570793.459229</v>
+        <v>1731573943.48742</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8980,11 +8980,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>Headers([('connection', 'Keep-Alive'), ('keep-alive', 'timeout=5, max=100'), ('x-powered-by', 'PHP/7.4.33'), ('set-cookie', 'frontend=50a5437b50d25974c8aa5d99345718ff; expires=Thu, 14-Nov-2024 09:42:15 GMT; Max-Age=3600; path=/; domain=www.zeminbank.com; HttpOnly; secure'), ('expires', 'Thu, 19 Nov 1981 08:52:00 GMT'), ('cache-control', 'no-store, no-cache, must-revalidate'), ('pragma', 'no-cache'), ('set-cookie', 'frontend_cid=RJ7EQlKcOA3DDrS2; expires=Thu, 14-Nov-2024 09:42:15 GMT; Max-Age=3600; path=/; domain=www.zeminbank.com; secure; HttpOnly'), ('set-cookie', 'store=tr_tr; expires=Fri, 14-Nov-2025 08:42:15 GMT; Max-Age=31536000; path=/; domain=www.zeminbank.com; HttpOnly; secure'), ('set-cookie', 'layout=deleted; expires=Thu, 01-Jan-1970 00:00:01 GMT; Max-Age=0; path=/; domain=www.zeminbank.com; HttpOnly; secure'), ('content-type', 'text/html; charset=UTF-8'), ('x-frame-options', 'SAMEORIGIN'), ('transfer-encoding', 'chunked'), ('content-encoding', 'br'), ('vary', 'Accept-Encoding,User-Agent'), ('date', 'Thu, 14 Nov 2024 08:42:15 GMT'), ('server', 'LiteSpeed'), ('x-content-type-options', 'nosniff'), ('x-xss-protection', '1; mode=block'), ('alt-svc', 'h3=":443"; ma=2592000, h3-29=":443"; ma=2592000, h3-Q050=":443"; ma=2592000, h3-Q046=":443"; ma=2592000, h3-Q043=":443"; ma=2592000, quic=":443"; ma=2592000; v="43,46"')])</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>2.003288269042969e-05</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -9004,77 +9004,77 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>130.107.146.159.srv.turk.net</t>
+          <t>ip128.ip-51-195-87.eu</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Hesse</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>41.0138,28.9497</t>
+          <t>50.1155,8.6842</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>AS12735 TurkNet Iletisim Hizmetleri A.S.</t>
+          <t>AS16276 OVH SAS</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>60306</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Europe/Istanbul</t>
+          <t>Europe/Berlin</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>TRY</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>41.0138</t>
+          <t>50.1155</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>28.9497</t>
+          <t>8.6842</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>https://cdn.ipinfo.io/static/images/countries-flags/TR.svg</t>
+          <t>https://cdn.ipinfo.io/static/images/countries-flags/DE.svg</t>
         </is>
       </c>
     </row>
